--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -4716,6 +4716,352 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>SIVE</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Sivers Semiconductor</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>SIVE.ST</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Optical / silicon photonics</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>CW/LPO laser arrays, laser light sources</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>Laser light-source supplier for co-packaged &amp; pluggable optics; GlobalFoundries SiPh partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>GlobalFoundries</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Foundry / Manufacturing</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>Specialty foundry / silicon photonics</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>Specialty wafers, silicon-photonics (SCALE) platform</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>Specialty foundry; silicon-photonics/CPO platform partner to optical-laser suppliers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>Custom CPU / edge AI</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>Snapdragon, Oryon (NUVIA) custom Arm CPUs, on-device AI</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>Arm-architecture licensee; custom CPUs and on-device/edge AI inference silicon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Cipher Mining</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Infrastructure (REITs)</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>HPC colocation / neocloud (AI + BTC)</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter capacity, HPC hosting</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>Bitcoin miner pivoting to AI/HPC datacenter capacity; peer of IREN/CORZ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr"/>
+      <c r="E88" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>AI Labs / Model Developers</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>Frontier AI lab</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>Grok models; Colossus GPU supercluster</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>Frontier AI lab and major GPU/networking buyer; named Credo AEC customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>2454.TW</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>Fabless SoC / custom ASIC</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>Mobile SoCs; custom AI ASIC (Google TPU collaboration)</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>Fabless designer co-developing a lower-cost Google TPU/ASIC; emerging custom-silicon competitor to Broadcom</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Entegris</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>Specialty materials &amp; purity solutions</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>Materials Solutions; Advanced Purity Solutions (filtration, fluids, gas/chem handling)</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>Supplies yield-critical specialty materials and purity solutions to foundries, IDMs and WFE makers</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4730,7 +5076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -6268,17 +6614,17 @@
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>Arista 7060X6/7800R4 switches powered by Broadcom Tomahawk 5 &amp; Jericho 3-AI silicon (FACT, NextPlatform/Arista)</t>
+          <t>Arista predominantly/sole-source reliant on Broadcom merchant silicon for switching chips; Tomahawk 5 &amp; Jericho 3-AI (FACT, ANET 10-K 2026-02-17; NextPlatform).</t>
         </is>
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>https://www.nextplatform.com/2024/08/21/arista-banks-on-the-ai-network-double-whammy/</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1596532/0001596532-26-000013-index.html</t>
         </is>
       </c>
     </row>
@@ -6395,17 +6741,17 @@
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Marvell custom silicon design win on Amazon Trainium (FACT, Tom's Hardware 2026)</t>
+          <t>Marvell custom AI silicon (XPU)/electro-optics for hyperscalers - Amazon Trainium program; data center largest end market (FACT, MRVL 10-K FY2026 2026-03-11).</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/custom-ai-asics-examined-from-broadcom-to-mtia</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
@@ -6440,17 +6786,17 @@
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Marvell co-designs Microsoft Maia custom AI silicon (FACT, Tom's Hardware 2026)</t>
+          <t>Marvell co-designs Microsoft Maia custom AI silicon; data center largest end market (FACT, MRVL 10-K FY2026 2026-03-11).</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/custom-ai-asics-examined-from-broadcom-to-mtia</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
@@ -7188,13 +7534,21 @@
       <c r="F58" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="15" t="n"/>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, AMD 10-K FY2025 2026-02-04): Instinct MI300-series accelerators deployed at scale by Microsoft.</t>
+        </is>
+      </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I58" s="15" t="n"/>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="9">
       <c r="A59" s="15" t="inlineStr">
@@ -7225,13 +7579,21 @@
       <c r="F59" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="15" t="n"/>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, AMD 10-K FY2025 2026-02-04): Instinct MI300-series accelerators deployed at scale by Meta.</t>
+        </is>
+      </c>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I59" s="15" t="n"/>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="9">
       <c r="A60" s="15" t="inlineStr">
@@ -7262,13 +7624,21 @@
       <c r="F60" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="15" t="n"/>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, AMD 10-K FY2025 2026-02-04): Instinct MI300-series accelerators deployed at scale by Oracle.</t>
+        </is>
+      </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I60" s="15" t="n"/>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="9">
       <c r="A61" s="15" t="inlineStr">
@@ -8490,7 +8860,11 @@
       <c r="F92" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G92" s="15" t="n"/>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply</t>
+        </is>
+      </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -8564,7 +8938,11 @@
       <c r="F94" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G94" s="15" t="n"/>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply</t>
+        </is>
+      </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -12571,6 +12949,726 @@
       <c r="H190" s="8" t="inlineStr">
         <is>
           <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>AAOI</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>Applied Optoelectronics</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>supplies optical transceivers to</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E191" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F191" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G191" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, AAOI 10-K 2026-02-26): Microsoft = largest internet data center customer at 28.8% of FY2025 revenue; top-10 customers = 96.6% (customer concentration).</t>
+        </is>
+      </c>
+      <c r="H191" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I191" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1158114/0001437749-26-005875-index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>SIVE</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>Sivers Semiconductor</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
+        <is>
+          <t>GlobalFoundries</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-02 via Reuters): silicon-photonics strategic collaboration; Sivers laser arrays integrated into GlobalFoundries SiPh reference designs for pluggables/CPO/LPO; joint $25B pluggable-optics TAM by 2030</t>
+        </is>
+      </c>
+      <c r="H192" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I192" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02-0746-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>SIVE</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>Sivers Semiconductor</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-02): supplies CW/LPO laser light sources for co-packaged &amp; pluggable optics</t>
+        </is>
+      </c>
+      <c r="H193" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I193" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02-0746-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>GlobalFoundries</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-02): silicon-photonics foundry (SCALE platform) for CPO/LPO/pluggables</t>
+        </is>
+      </c>
+      <c r="H194" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I194" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02-0746-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>licenses CPU IP to</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-02): Qualcomm is an Arm-architecture licensee; custom Oryon/NUVIA CPUs</t>
+        </is>
+      </c>
+      <c r="H195" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I195" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02-1634-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D196" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E196" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F196" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-02): on-device / edge AI inference silicon</t>
+        </is>
+      </c>
+      <c r="H196" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I196" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02-1634-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D197" s="8" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="E197" s="8" t="inlineStr">
+        <is>
+          <t>Marvell</t>
+        </is>
+      </c>
+      <c r="F197" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-02): NVIDIA $2B strategic investment in Marvell; Jensen Computex 'next $1T' endorsement</t>
+        </is>
+      </c>
+      <c r="H197" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I197" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02-1634-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>Cipher Mining</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-02): crypto-miner pivoting to AI/HPC capacity amid compute-shortage narrative</t>
+        </is>
+      </c>
+      <c r="H198" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I198" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-02-0746-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>Credo Technology</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>supplies AECs to</t>
+        </is>
+      </c>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G199" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-06-02): top-3 10%+ Credo customer in FQ4; AECs core growth engine; allocation tight</t>
+        </is>
+      </c>
+      <c r="H199" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I199" s="8" t="inlineStr">
+        <is>
+          <t>TMTB 早报 - TMT Breakout --- TMTB Morning Wrap - TMT Breakout(17).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>Credo Technology</t>
+        </is>
+      </c>
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>supplies AECs to</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E200" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G200" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-06-02): 10%+ Credo customer in FQ4; AEC adoption broadening</t>
+        </is>
+      </c>
+      <c r="H200" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I200" s="8" t="inlineStr">
+        <is>
+          <t>TMTB 早报 - TMT Breakout --- TMTB Morning Wrap - TMT Breakout(17).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>Credo Technology</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>supplies AECs to</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="E201" s="8" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G201" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-06-02): top-3 10%+ Credo customer in FQ4</t>
+        </is>
+      </c>
+      <c r="H201" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I201" s="8" t="inlineStr">
+        <is>
+          <t>TMTB 早报 - TMT Breakout --- TMTB Morning Wrap - TMT Breakout(17).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Morgan Stanley 2026-06-01): Google working with MediaTek on a lower-cost TPU/ASIC, ramp as soon as 2027</t>
+        </is>
+      </c>
+      <c r="H202" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I202" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Semiconductors：Takeaways from our meetings in Taiwan-260601.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>competes with</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-01): MediaTek targets 15-20% of Google ASIC; Broadcom expects to keep 80%+ share — second-source threat</t>
+        </is>
+      </c>
+      <c r="H203" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I203" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Semiconductors：Takeaways from our meetings in Taiwan-260601.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>competes with</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Morgan Stanley 2026-06-01): NVIDIA targeting ~$20bn CPU (Grace/Vera Arm) vs x86 server CPUs; CPU supply tight</t>
+        </is>
+      </c>
+      <c r="H204" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I204" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Semiconductors：Takeaways from our meetings in Taiwan-260601.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>manufactures chips for</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E205" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-01): critical Intel roadmap parts (desktop, possibly server Rapids) likely move to TSMC; EMIB-T users see TSMC as plan B</t>
+        </is>
+      </c>
+      <c r="H205" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I205" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Semiconductors：Takeaways from our meetings in Taiwan-260601.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
+        <is>
+          <t>Entegris</t>
+        </is>
+      </c>
+      <c r="C206" s="8" t="inlineStr">
+        <is>
+          <t>supplies materials to</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="E206" s="8" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="F206" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Bernstein 2026-06-02): yield-critical specialty/purity materials; foundries are main customers</t>
+        </is>
+      </c>
+      <c r="H206" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I206" s="8" t="inlineStr">
+        <is>
+          <t>Bernstein-U.S. Semiconductors and Semicap Equipment： Conversations with 5 CEOs at Bernstein's 2026 Strategic Decisions Conference-260602.pdf</t>
         </is>
       </c>
     </row>
@@ -12851,7 +13949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12903,65 +14001,65 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -12984,21 +14082,21 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T_TRAIN</t>
+          <t>T_INFER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AI Training Capex</t>
+          <t>AI Inference Demand</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13010,21 +14108,21 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T_INFER</t>
+          <t>T_TRAIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AI Inference Demand</t>
+          <t>AI Training Capex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13071,50 +14169,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>T_CPO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Co-Packaged Optics (CPO)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T_CPO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Co-Packaged Optics (CPO)</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>11</v>
@@ -13140,10 +14238,10 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -13166,33 +14264,33 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T_CHINA</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>China Indigenous AI Buildout</t>
+          <t>Marvell</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
@@ -13201,76 +14299,76 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marvell</t>
+          <t>Alphabet (Google)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>T_CHINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>China Indigenous AI Buildout</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alphabet (Google)</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -13279,24 +14377,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
@@ -13305,24 +14403,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T_GLASS</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Glass Core Substrate</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
         <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
@@ -13331,43 +14429,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>T_GLASS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Glass Core Substrate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -13383,12 +14481,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -13397,10 +14495,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -13409,24 +14507,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -13435,17 +14533,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -13461,24 +14559,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -13487,12 +14585,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13513,24 +14611,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -13539,24 +14637,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T_HBM</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HBM Demand</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -13565,24 +14663,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>T_HBM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>HBM Demand</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -13591,24 +14689,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -13617,76 +14715,76 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -13695,24 +14793,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -13735,88 +14833,88 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -13825,24 +14923,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -13851,24 +14949,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -13877,24 +14975,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -13903,24 +15001,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -13929,24 +15027,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -13955,24 +15053,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -13981,17 +15079,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -14007,24 +15105,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
@@ -14033,24 +15131,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -14059,12 +15157,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14073,10 +15171,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -14085,24 +15183,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
@@ -14111,24 +15209,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -14137,24 +15235,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
         <v>3</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -14163,12 +15261,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14189,24 +15287,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -14215,17 +15313,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -14241,24 +15339,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -14267,24 +15365,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -14293,43 +15391,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -14345,17 +15443,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -14735,121 +15833,121 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -14865,24 +15963,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
         <v>1</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -14891,24 +15989,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
         <v>1</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -14917,24 +16015,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
         <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -14943,17 +16041,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -14969,17 +16067,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -14995,12 +16093,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -15015,6 +16113,188 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>HUAWEI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Teradyne</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>XLIGHT</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>XLight</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sandisk</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cipher Mining</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Datacenter Infrastructure (REITs)</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AI Labs / Model Developers</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Entegris</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -5062,6 +5062,256 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>AYAR</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Ayar Labs</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>Co-packaged optics (CPO)</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>Optical I/O chiplets, CPO for AI scale-up</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA-backed CPO supplier in NVLink Fusion ecosystem for rack-scale optical interconnect</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>Silicon photonics / optical + power semi</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Silicon-photonic PICs, BiCMOS EICs, power semis</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>Supplies datacenter optical-engine components; ramping AI-driven DC revenue (~$1B 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>NANYA</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Nanya Technology</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>2408.TW</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>Commodity DRAM, DDR5, specialty DRAM</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan DRAM maker riding the AI-driven memory price upcycle; potential HBM/specialty expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Astera Labs</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity / SerDes / retimers</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>Aries retimers, Scorpio fabric switches, UALink/PCIe/CXL connectivity</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>AI rack-scale connectivity supplier; scale-up switching for Trainium/UALink deployments</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>SMTC</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Semtech</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>SMTC</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>Optical/copper interconnect ICs</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>CopperEdge ACCs, FiberEdge TIAs/drivers, HieFo gain chips</t>
+        </is>
+      </c>
+      <c r="J95" s="8" t="inlineStr">
+        <is>
+          <t>Supplies 800G/1.6T optical &amp; active-copper interconnect components for AI datacenters</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5076,7 +5326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -13669,6 +13919,906 @@
       <c r="I206" s="8" t="inlineStr">
         <is>
           <t>Bernstein-U.S. Semiconductors and Semicap Equipment： Conversations with 5 CEOs at Bernstein's 2026 Strategic Decisions Conference-260602.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>AYAR</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>Ayar Labs</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>supplies optical components to</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E207" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F207" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G207" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-03): Ayar Labs in NVIDIA NVLink Fusion ecosystem; CPO optically/electrically compatible with NVIDIA optics/SerDes; NVIDIA backed $500M Series E</t>
+        </is>
+      </c>
+      <c r="H207" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I207" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-03-0734-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>AYAR</t>
+        </is>
+      </c>
+      <c r="B208" s="8" t="inlineStr">
+        <is>
+          <t>Ayar Labs</t>
+        </is>
+      </c>
+      <c r="C208" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E208" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F208" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G208" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-03): Ayar Labs co-packaged-optics supplier bringing CPO to rack-scale AI via NVLink Fusion</t>
+        </is>
+      </c>
+      <c r="H208" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I208" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-03-0734-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F209" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-03): STMicro raised 2026 datacenter rev to ~$1B, ~2/3 from optical components (silicon-photonic PICs, BiCMOS EICs)</t>
+        </is>
+      </c>
+      <c r="H209" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I209" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-03-0734-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="B210" s="8" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="C210" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D210" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F210" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-03): STMicro datacenter revenue ramp driven by AI-infrastructure demand; guidance could double in 2027</t>
+        </is>
+      </c>
+      <c r="H210" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I210" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-03-0734-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E211" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F211" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Mizuho 2026-05-19): AI rack 800V power architectures drive analog/power-semi content growth; rising lead times</t>
+        </is>
+      </c>
+      <c r="H211" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I211" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0519_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
+        <is>
+          <t>NANYA</t>
+        </is>
+      </c>
+      <c r="B212" s="8" t="inlineStr">
+        <is>
+          <t>Nanya Technology</t>
+        </is>
+      </c>
+      <c r="C212" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D212" s="8" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E212" s="8" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F212" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G212" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-03): Nanya May revenue +730% YoY to NT$27.7B, 7th straight monthly record, on AI-driven DRAM price surge</t>
+        </is>
+      </c>
+      <c r="H212" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I212" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-03-2229-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>NANYA</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>Nanya Technology</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>supplies memory to</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="E213" s="8" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="F213" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-05-15): Cisco cited a Nanya DRAM supply agreement to secure memory through CY26</t>
+        </is>
+      </c>
+      <c r="H213" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I213" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0515_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>ANTHROPIC</t>
+        </is>
+      </c>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G214" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, GS 2026-06-03): Broadcom ramping initial 1GW Anthropic custom-silicon capacity, +5GW from FY27; one of 6 custom-silicon engagements</t>
+        </is>
+      </c>
+      <c r="H214" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I214" s="8" t="inlineStr">
+        <is>
+          <t>博通 Strong AI revenue momentum for 2027.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="E215" s="8" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="F215" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, GS 2026-06-03): OpenAI among Broadcom's six custom-silicon engagements ramping into FY27</t>
+        </is>
+      </c>
+      <c r="H215" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I215" s="8" t="inlineStr">
+        <is>
+          <t>博通 Strong AI revenue momentum for 2027.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="B216" s="8" t="inlineStr">
+        <is>
+          <t>Lumentum</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>supplies optical components to</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E216" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F216" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G216" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, LITE CEO @JPM 2026-05): NVIDIA locked up a considerable share of Lumentum indium-phosphide (InP) laser capacity with options to take more; capacity tight/locked</t>
+        </is>
+      </c>
+      <c r="H216" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I216" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0519_wrap.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>Astera Labs</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>supplies interconnect to</t>
+        </is>
+      </c>
+      <c r="D217" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="E217" s="8" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F217" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-05): Astera Labs scale-up/UALink connectivity into AWS Trainium deployments ramping 2027</t>
+        </is>
+      </c>
+      <c r="H217" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I217" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0520_wrap.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B218" s="8" t="inlineStr">
+        <is>
+          <t>Astera Labs</t>
+        </is>
+      </c>
+      <c r="C218" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E218" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F218" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G218" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-05): scale-up switching (Scorpio), retimers, UALink for AI racks; Scorpio CY27 content $6.5-7B per SemiAnalysis</t>
+        </is>
+      </c>
+      <c r="H218" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I218" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0520_wrap.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>Astera Labs</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E219" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F219" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G219" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, ISI 2026-05): scale-up switch demand growing for inference clusters</t>
+        </is>
+      </c>
+      <c r="H219" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I219" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0519_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="B220" s="8" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C220" s="8" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="E220" s="8" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F220" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G220" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-05): OpenAI committed to renting large amounts of current/future AWS Trainium capacity</t>
+        </is>
+      </c>
+      <c r="H220" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I220" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0520_wrap.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E221" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F221" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-06-03): Intel delivering Infrastructure Processing Unit (IPU) for Google; designed and already being deployed</t>
+        </is>
+      </c>
+      <c r="H221" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I221" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0603_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B222" s="8" t="inlineStr">
+        <is>
+          <t>Marvell</t>
+        </is>
+      </c>
+      <c r="C222" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D222" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E222" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F222" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Funda-AI 2026-06-03): Marvell to design the networking chip in the Google/Intel IPU program (?)</t>
+        </is>
+      </c>
+      <c r="H222" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I222" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0603_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>Bloom Energy</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>supplies on-site fuel-cell power to</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="E223" s="8" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="F223" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Goldman 2026-05-28): Bloom Energy partnership accelerates Nebius power permitting/deployment (800MW-1GW connected 2026)</t>
+        </is>
+      </c>
+      <c r="H223" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I223" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0528_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>SMTC</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>Semtech</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E224" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F224" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G224" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-05-27): Semtech 800G FiberEdge &amp; 1.6T design wins incl some sole-source sockets; shipping 1.6T CopperEdge ICs for a US hyperscaler; HieFo gain-chip demand ~3x supply</t>
+        </is>
+      </c>
+      <c r="H224" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I224" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0527_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>SMTC</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>Semtech</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F225" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G225" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, TMTB 2026-05-27): DWDM/CPO laser engagements as CPO ramps</t>
+        </is>
+      </c>
+      <c r="H225" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I225" s="8" t="inlineStr">
+        <is>
+          <t>TMTB0527_morning.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B226" s="8" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C226" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E226" s="8" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F226" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G226" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, GS 2026-06-04): High-NA adoption in memory + DRAM EUV/DUV layer growth driven by AI/HBM memory demand</t>
+        </is>
+      </c>
+      <c r="H226" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I226" s="8" t="inlineStr">
+        <is>
+          <t>ASML.pdf</t>
         </is>
       </c>
     </row>
@@ -13949,7 +15099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14004,99 +15154,99 @@
         <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>T_INFER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>AI Inference Demand</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T_INFER</t>
+          <t>T_CPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AI Inference Demand</t>
+          <t>Co-Packaged Optics (CPO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14108,36 +15258,36 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T_TRAIN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AI Training Capex</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -14160,21 +15310,21 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T_CPO</t>
+          <t>T_TRAIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Co-Packaged Optics (CPO)</t>
+          <t>AI Training Capex</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14195,12 +15345,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14209,140 +15359,140 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marvell</t>
+          <t>Alphabet (Google)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alphabet (Google)</t>
+          <t>Marvell</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T_CHINA</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>China Indigenous AI Buildout</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
@@ -14351,76 +15501,76 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>T_HBM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>HBM Demand</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>T_CHINA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>China Indigenous AI Buildout</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
@@ -14429,24 +15579,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T_GLASS</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Glass Core Substrate</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
@@ -14455,64 +15605,64 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>T_GLASS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>Glass Core Substrate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14521,10 +15671,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -14533,24 +15683,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -14559,17 +15709,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -14585,24 +15735,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -14611,12 +15761,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -14637,24 +15787,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -14663,24 +15813,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T_HBM</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HBM Demand</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -14689,24 +15839,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -14715,24 +15865,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -14741,24 +15891,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -14767,38 +15917,38 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14819,12 +15969,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Arm Holdings</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14845,24 +15995,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Arm Holdings</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
@@ -14871,12 +16021,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14897,116 +16047,116 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
         <v>3</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15015,36 +16165,36 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -15053,17 +16203,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -15079,24 +16229,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -15105,17 +16255,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -15131,24 +16281,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -15157,24 +16307,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -15183,12 +16333,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -15209,12 +16359,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15223,10 +16373,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -15235,24 +16385,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
         <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>3</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -15261,24 +16411,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -15287,12 +16437,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -15301,10 +16451,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -15313,12 +16463,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -15327,10 +16477,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -15339,17 +16489,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -15391,17 +16541,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -15417,64 +16567,64 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15483,24 +16633,24 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15521,17 +16671,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -15547,17 +16697,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -15573,17 +16723,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -15599,17 +16749,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -15625,17 +16775,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -15651,17 +16801,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -15677,17 +16827,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -15703,12 +16853,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15729,17 +16879,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -15755,17 +16905,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -15781,17 +16931,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -15807,17 +16957,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -15833,17 +16983,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -15859,24 +17009,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -15885,24 +17035,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -15911,24 +17061,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -15937,147 +17087,147 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="n">
         <v>0</v>
       </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="n">
         <v>0</v>
       </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -16093,24 +17243,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
         <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -16119,17 +17269,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -16145,17 +17295,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -16171,17 +17321,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -16197,17 +17347,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -16223,17 +17373,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cipher Mining</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -16249,17 +17399,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -16275,12 +17425,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -16295,6 +17445,136 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>XLIGHT</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>XLight</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sandisk</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cipher Mining</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Datacenter Infrastructure (REITs)</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AI Labs / Model Developers</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Entegris</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -5312,6 +5312,156 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>SAMBANOVA</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>(private)</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>AI accelerators / RDU</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>Reconfigurable Dataflow Units, inference systems</t>
+        </is>
+      </c>
+      <c r="J96" s="8" t="inlineStr">
+        <is>
+          <t>AI-chip designer pairing rack-scale inference systems with Intel Xeon hosts</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>BYTEDANCE</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>(private)</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscaler (China)</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>TikTok/Doubao, AI datacenters</t>
+        </is>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>China hyperscaler adopting Arm AGI CPU for AI datacenter deployments</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>Neocloud / compute capacity</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>Colossus AI datacenters (Memphis); GPU compute rental</t>
+        </is>
+      </c>
+      <c r="J98" s="8" t="inlineStr">
+        <is>
+          <t>Musk-linked neocloud renting NVDA-GPU compute to Google &amp; Anthropic; IPO ~Jun-2026 (?) Colossus commonly associated with xAI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5326,7 +5476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I226"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -6602,15 +6752,19 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Lead HBM supplier</t>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified SK Hynix for Vera Rubin HBM4 supply (est 60-70% of volume); press-corroborated; lead HBM supplier</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I30" s="15" t="n"/>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="9">
       <c r="A31" s="15" t="inlineStr">
@@ -6909,15 +7063,19 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>TPU partner</t>
+          <t>(FACT, X-scan 2026-06-05): AVGO Q2 FY26 call - Google TPU commitment 'remains substantial' despite supplier diversification</t>
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="n"/>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="9">
       <c r="A38" s="15" t="inlineStr">
@@ -14819,6 +14977,546 @@
       <c r="I226" s="8" t="inlineStr">
         <is>
           <t>ASML.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>FOXCONN</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>Foxconn (Hon Hai)</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F227" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-04): Hon Hai (Foxconn) and Intel announced strategic collaboration on next-gen AI infrastructure, Edge AI, and Physical AI</t>
+        </is>
+      </c>
+      <c r="H227" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I227" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-04-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>SAMBANOVA</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="C228" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E228" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F228" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-04): SambaNova AI platform paired with Intel Xeon processors in rack-scale infrastructure for hyperscale deployments, disclosed alongside the Foxconn–Intel Computex 2026 announcement.</t>
+        </is>
+      </c>
+      <c r="H228" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I228" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-04-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F229" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G229" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): C.C. Wei at 6/4 AGM guided 2026 revenue growth &gt;30% USD and 2026 capex near upper end of $52-56B, citing agentic-AI compute/token demand.</t>
+        </is>
+      </c>
+      <c r="H229" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="I229" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>supplies HBM to</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G230" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified Micron for Vera Rubin HBM4 supply; press-corroborated</t>
+        </is>
+      </c>
+      <c r="H230" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I230" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>supplies HBM to</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F231" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G231" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified Samsung for Vera Rubin HBM4 supply; press-corroborated</t>
+        </is>
+      </c>
+      <c r="H231" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I231" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B232" s="8" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C232" s="8" t="inlineStr">
+        <is>
+          <t>licenses CPU IP to</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="E232" s="8" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="F232" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G232" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): Meta named Arm AGI-CPU customer; Arm CEO at Computex, press-corroborated</t>
+        </is>
+      </c>
+      <c r="H232" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I232" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>licenses CPU IP to</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="F233" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G233" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): OpenAI in Arm AGI-CPU customer roster; press-corroborated</t>
+        </is>
+      </c>
+      <c r="H233" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I233" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>licenses CPU IP to</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="E234" s="8" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="F234" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G234" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): Oracle named Arm AGI-CPU adopter at Computex; press-corroborated</t>
+        </is>
+      </c>
+      <c r="H234" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I234" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>licenses CPU IP to</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>BYTEDANCE</t>
+        </is>
+      </c>
+      <c r="E235" s="8" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="F235" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G235" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): ByteDance named Arm AGI-CPU adopter at Computex; press-corroborated</t>
+        </is>
+      </c>
+      <c r="H235" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I235" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="E236" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="F236" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G236" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): Google to rent ~$30B / ~110k NVDA-GPU compute capacity from SpaceX (Colossus), $920M/mo Oct-2026-&gt;Jun-2029; multi-press (?) Colossus usually attributed to xAI</t>
+        </is>
+      </c>
+      <c r="H236" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I236" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>ANTHROPIC</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="F237" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G237" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): Anthropic ~$45B multiyear compute deal across SpaceX Colossus / Colossus II ($1.25B/mo through May-2029) (?) Colossus usually attributed to xAI</t>
+        </is>
+      </c>
+      <c r="H237" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I237" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C238" s="8" t="inlineStr">
+        <is>
+          <t>sells GPUs to</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="E238" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="F238" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G238" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-05): SpaceX Colossus deploys ~110k NVIDIA GPUs to serve the Google compute contract (?) Colossus usually attributed to xAI</t>
+        </is>
+      </c>
+      <c r="H238" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I238" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-05-2004-x-scan.md</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15151,36 +15849,36 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
@@ -15189,27 +15887,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -15232,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -15437,114 +16135,114 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marvell</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Arm Holdings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T_HBM</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HBM Demand</t>
+          <t>Marvell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T_CHINA</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>China Indigenous AI Buildout</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
@@ -15553,76 +16251,76 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>T_HBM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>HBM Demand</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>T_CHINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>China Indigenous AI Buildout</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -15631,17 +16329,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T_GLASS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Glass Core Substrate</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -15657,128 +16355,128 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>T_GLASS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Glass Core Substrate</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -15787,24 +16485,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
         <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -15813,24 +16511,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -15839,24 +16537,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -15865,24 +16563,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -15891,24 +16589,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
         <v>3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -15917,24 +16615,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -15943,64 +16641,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Arm Holdings</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16021,17 +16719,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -16047,24 +16745,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
         <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3</v>
       </c>
       <c r="F37" t="n">
         <v>4</v>
@@ -16073,24 +16771,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
@@ -16099,24 +16797,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
@@ -16125,17 +16823,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -16151,24 +16849,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -16177,50 +16875,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -16307,17 +17005,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -16333,24 +17031,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
@@ -16359,12 +17057,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -16385,12 +17083,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16399,10 +17097,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -16411,24 +17109,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
         <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -16437,24 +17135,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -16463,12 +17161,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16477,10 +17175,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -16489,12 +17187,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16503,10 +17201,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -16515,17 +17213,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -16541,24 +17239,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -16567,17 +17265,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -16593,17 +17291,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -16619,12 +17317,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16645,69 +17343,69 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>SpaceX (Colossus compute)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -16723,17 +17421,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -16749,12 +17447,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16775,17 +17473,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -16801,17 +17499,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -16827,17 +17525,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -16853,17 +17551,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -16879,17 +17577,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -16905,17 +17603,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -16931,12 +17629,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -16957,17 +17655,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -16983,17 +17681,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -17009,17 +17707,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -17035,12 +17733,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17061,24 +17759,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -17087,17 +17785,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -17113,12 +17811,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17127,10 +17825,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -17139,17 +17837,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -17165,17 +17863,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NANYA</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -17191,17 +17889,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -17217,50 +17915,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
         <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -17269,17 +17967,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -17295,24 +17993,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
         <v>1</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -17321,17 +18019,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -17347,12 +18045,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -17373,17 +18071,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -17399,24 +18097,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
         <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -17425,24 +18123,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
         <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -17451,12 +18149,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -17477,17 +18175,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>XLIGHT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>XLight</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -17503,17 +18201,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cipher Mining</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -17529,24 +18227,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Cipher Mining</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
         <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -17555,26 +18253,104 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AI Labs / Model Developers</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Entegris</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Semiconductor Equipment</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>0</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SAMBANOVA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BYTEDANCE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -5462,6 +5462,306 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>0981.HK</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Foundry / Manufacturing</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>Foundry</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>Logic foundry (DUV multi-patterning advanced nodes)</t>
+        </is>
+      </c>
+      <c r="J99" s="8" t="inlineStr">
+        <is>
+          <t>China's leading-edge foundry; critical enabler of Huawei/Cambricon domestic AI chips</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>CAMBRICON</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Cambricon</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>688256.SS</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>AI Accelerators</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>Cloud AI inference/training accelerators</t>
+        </is>
+      </c>
+      <c r="J100" s="8" t="inlineStr">
+        <is>
+          <t>Leading Chinese AI GPGPU/ASIC vendor for indigenous AI buildout</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>LARGAN</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Largan Precision</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>3008.TW</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>Optical Components</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>Precision lenses; Fiber Array for CPO</t>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>Fiber Array coupling for silicon photonics; CPO supply-chain bottleneck</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>ZDT</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Zhen Ding Technology</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>4958.TW</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>PCB &amp; Substrate</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>HDI/mSAP PCB, ABF substrate, optical-module PCB</t>
+        </is>
+      </c>
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t>AI-server PCB &amp; ABF substrate supplier; optical-module mSAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>WIWYNN</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Wiwynn</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>6669.TW</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>ODM (AI servers/racks)</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscale AI servers &amp; CPO racks</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t>ODM integrating optical-I/O CPO racks (Ayar/GUC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>CAMT</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Camtek</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>CAMT</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>Inspection / Metrology</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>AP/HBM inspection systems (Eagle/Hawk)</t>
+        </is>
+      </c>
+      <c r="J104" s="8" t="inlineStr">
+        <is>
+          <t>Advanced-packaging &amp; HBM inspection equipment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5476,7 +5776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I238"/>
+  <dimension ref="A1:I258"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -7108,7 +7408,7 @@
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>MTIA</t>
+          <t>MTIA; (FACT, X-scan 2026-06-06): Broadcom Q2 FY26 multi-year hyperscaler custom-accelerator orders</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
@@ -7116,7 +7416,11 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="I38" s="15" t="n"/>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-06-2256-x-scan.md</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="9">
       <c r="A39" s="15" t="inlineStr">
@@ -15517,6 +15821,906 @@
       <c r="I238" s="8" t="inlineStr">
         <is>
           <t>X-Reports/2026-06-05-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>FOXCONN</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>Foxconn (Hon Hai)</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F239" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G239" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Citi 2026-06): builds NVIDIA Spectrum-6 SPX scale-out CPO rack; expanding Taiwan CPO supply chain</t>
+        </is>
+      </c>
+      <c r="H239" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I239" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Taiwan Semiconductors and Electronic Components &amp; Equipment：What’s New at COMPUTEX 2026， Part Two~CPO Ready to Go-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="B240" s="8" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="C240" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D240" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E240" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F240" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G240" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06): growing Ayar Labs CPO partnership; targets CPO solution in 2-3 yrs</t>
+        </is>
+      </c>
+      <c r="H240" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I240" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Taiwan Semiconductors and Electronic Components &amp; Equipment：What’s New at COMPUTEX 2026， Part Two~CPO Ready to Go-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F241" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G241" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Citi 2026-06): COUPE packaging + chip testing for CPO</t>
+        </is>
+      </c>
+      <c r="H241" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I241" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Taiwan Semiconductors and Electronic Components &amp; Equipment：What’s New at COMPUTEX 2026， Part Two~CPO Ready to Go-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="8" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>drives demand for</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E242" s="8" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F242" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G242" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Jefferies 2026-06): TPUv8 higher HBM content; HBM a pass-through cost</t>
+        </is>
+      </c>
+      <c r="H242" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I242" s="8" t="inlineStr">
+        <is>
+          <t>Jefferies-USA _ Semiconductors：Blayne’s Bytes： Optical Model Increase， Google Equity Raise， CRDO CEO Pay Plan-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>drives demand for</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E243" s="8" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F243" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G243" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Jefferies 2026-06): $85bn equity raise to fund AI compute; C26 capex $180-190bn, C27 higher</t>
+        </is>
+      </c>
+      <c r="H243" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I243" s="8" t="inlineStr">
+        <is>
+          <t>Jefferies-USA _ Semiconductors：Blayne’s Bytes： Optical Model Increase， Google Equity Raise， CRDO CEO Pay Plan-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>CAMBRICON</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
+          <t>Cambricon</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
+        <is>
+          <t>T_CHINA</t>
+        </is>
+      </c>
+      <c r="E244" s="8" t="inlineStr">
+        <is>
+          <t>China Indigenous AI Buildout</t>
+        </is>
+      </c>
+      <c r="F244" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G244" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, MS/Bernstein 2026-06): leading China AI GPGPU inference, OW; strong customer anchoring</t>
+        </is>
+      </c>
+      <c r="H244" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I244" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Build for Future AI Infrastructure – CPU， GPU， ASIC， Optical， and China Chip.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>CAMBRICON</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>Cambricon</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>competes with</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E245" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F245" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G245" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, MS 2026-06): domestic GPGPU alternative; lower TCO for China inference</t>
+        </is>
+      </c>
+      <c r="H245" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I245" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Build for Future AI Infrastructure – CPU， GPU， ASIC， Optical， and China Chip.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D246" s="8" t="inlineStr">
+        <is>
+          <t>T_CHINA</t>
+        </is>
+      </c>
+      <c r="E246" s="8" t="inlineStr">
+        <is>
+          <t>China Indigenous AI Buildout</t>
+        </is>
+      </c>
+      <c r="F246" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G246" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06): critical leading-edge foundry enabler for Huawei advanced logic; sole domestic advanced foundry</t>
+        </is>
+      </c>
+      <c r="H246" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I246" s="8" t="inlineStr">
+        <is>
+          <t>20260604-Bernstein-China Semis： Huawei's LogicFolding， an underestimated breakthrough.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>manufactures chips for</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="inlineStr">
+        <is>
+          <t>HUAWEI</t>
+        </is>
+      </c>
+      <c r="E247" s="8" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="F247" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G247" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06): domestic DUV multi-patterning advanced-logic foundry for Huawei (China indigenous)</t>
+        </is>
+      </c>
+      <c r="H247" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I247" s="8" t="inlineStr">
+        <is>
+          <t>20260604-Bernstein-China Semis： Huawei's LogicFolding， an underestimated breakthrough.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
+          <t>SMIC</t>
+        </is>
+      </c>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>manufactures chips for</t>
+        </is>
+      </c>
+      <c r="D248" s="8" t="inlineStr">
+        <is>
+          <t>CAMBRICON</t>
+        </is>
+      </c>
+      <c r="E248" s="8" t="inlineStr">
+        <is>
+          <t>Cambricon</t>
+        </is>
+      </c>
+      <c r="F248" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G248" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, MS 2026-06): domestic foundry for China AI GPGPU (?)</t>
+        </is>
+      </c>
+      <c r="H248" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I248" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Build for Future AI Infrastructure – CPU， GPU， ASIC， Optical， and China Chip.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>AYAR</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t>Ayar Labs</t>
+        </is>
+      </c>
+      <c r="F249" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G249" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Citi 2026-06): MediaTek + Ayar Labs CPO partnership (advanced I/O, chiplet, ASIC + optical engine)</t>
+        </is>
+      </c>
+      <c r="H249" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I249" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Taiwan Semiconductors and Electronic Components &amp; Equipment：What’s New at COMPUTEX 2026， Part Two~CPO Ready to Go-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="8" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D250" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E250" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F250" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G250" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, MS 2026-06): 20-core customized Grace CPU for NVIDIA N1X AI PC (RTX Spark)</t>
+        </is>
+      </c>
+      <c r="H250" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I250" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Build for Future AI Infrastructure – CPU， GPU， ASIC， Optical， and China Chip.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>WIWYNN</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>Wiwynn</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D251" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E251" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F251" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G251" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Citi 2026-06): demoed optical-I/O CPO rack with Ayar Labs &amp; GUC</t>
+        </is>
+      </c>
+      <c r="H251" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I251" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Taiwan Semiconductors and Electronic Components &amp; Equipment：What’s New at COMPUTEX 2026， Part Two~CPO Ready to Go-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="8" t="inlineStr">
+        <is>
+          <t>LARGAN</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="inlineStr">
+        <is>
+          <t>Largan Precision</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D252" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E252" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F252" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G252" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06): Fiber Array micron-level alignment - key CPO bottleneck; sample by end-2026</t>
+        </is>
+      </c>
+      <c r="H252" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I252" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Taiwan Semiconductors and Electronic Components &amp; Equipment：What’s New at COMPUTEX 2026， Part Two~CPO Ready to Go-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>CAMT</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>Camtek</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E253" s="8" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F253" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G253" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Jefferies 2026-06): $50M+ Hawk inspection orders from leading HBM player; AI-related, delivered C27</t>
+        </is>
+      </c>
+      <c r="H253" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I253" s="8" t="inlineStr">
+        <is>
+          <t>Jefferies-USA _ Semiconductors：Blayne’s Bytes： Optical Model Increase， Google Equity Raise， CRDO CEO Pay Plan-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="8" t="inlineStr">
+        <is>
+          <t>ZDT</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="inlineStr">
+        <is>
+          <t>Zhen Ding Technology</t>
+        </is>
+      </c>
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D254" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E254" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F254" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G254" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06): mSAP optical-module PCB for 800G/1.6T transceivers; aggressive capacity expansion</t>
+        </is>
+      </c>
+      <c r="H254" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I254" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Zhen Ding Technology （4958.TW） Optical module and substrate on the rise； upgrade to Buy-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>ZDT</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>Zhen Ding Technology</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>supplies ABF substrate to</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="E255" s="8" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="F255" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G255" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06): ABF substrate for MediaTek-handled Google TPU from 4Q26E</t>
+        </is>
+      </c>
+      <c r="H255" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I255" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Zhen Ding Technology （4958.TW） Optical module and substrate on the rise； upgrade to Buy-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="8" t="inlineStr">
+        <is>
+          <t>ZDT</t>
+        </is>
+      </c>
+      <c r="B256" s="8" t="inlineStr">
+        <is>
+          <t>Zhen Ding Technology</t>
+        </is>
+      </c>
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>supplies ABF substrate to</t>
+        </is>
+      </c>
+      <c r="D256" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E256" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F256" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G256" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06): ABF substrate client in queue (?)</t>
+        </is>
+      </c>
+      <c r="H256" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I256" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Zhen Ding Technology （4958.TW） Optical module and substrate on the rise； upgrade to Buy-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>ZDT</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>Zhen Ding Technology</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>supplies ABF substrate to</t>
+        </is>
+      </c>
+      <c r="D257" s="8" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="E257" s="8" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="F257" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G257" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06): ABF substrate client in queue (?)</t>
+        </is>
+      </c>
+      <c r="H257" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I257" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Zhen Ding Technology （4958.TW） Optical module and substrate on the rise； upgrade to Buy-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="8" t="inlineStr">
+        <is>
+          <t>ZDT</t>
+        </is>
+      </c>
+      <c r="B258" s="8" t="inlineStr">
+        <is>
+          <t>Zhen Ding Technology</t>
+        </is>
+      </c>
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>supplies ABF substrate to</t>
+        </is>
+      </c>
+      <c r="D258" s="8" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="E258" s="8" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="F258" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G258" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06): ABF substrate client in queue (?)</t>
+        </is>
+      </c>
+      <c r="H258" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="I258" s="8" t="inlineStr">
+        <is>
+          <t>CITI-Zhen Ding Technology （4958.TW） Optical module and substrate on the rise； upgrade to Buy-260605.pdf</t>
         </is>
       </c>
     </row>
@@ -15797,7 +17001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15852,73 +17056,73 @@
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>T_CPO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Co-Packaged Optics (CPO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T_INFER</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI Inference Demand</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15930,21 +17134,21 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T_CPO</t>
+          <t>T_INFER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Co-Packaged Optics (CPO)</t>
+          <t>AI Inference Demand</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15956,10 +17160,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -15991,24 +17195,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T_POWER</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Datacenter Power Demand</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
@@ -16034,36 +17238,36 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>T_POWER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Datacenter Power Demand</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -16135,13 +17339,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -16173,128 +17377,128 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>T_HBM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arm Holdings</t>
+          <t>HBM Demand</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>T_CHINA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Marvell</t>
+          <t>China Indigenous AI Buildout</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>Arm Holdings</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T_HBM</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HBM Demand</t>
+          <t>Marvell</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T_CHINA</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>China Indigenous AI Buildout</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
@@ -16459,38 +17663,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -16499,10 +17703,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -16511,24 +17715,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -16537,17 +17741,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -16563,24 +17767,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -16589,24 +17793,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -16615,24 +17819,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -16641,24 +17845,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -16667,24 +17871,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -16693,76 +17897,76 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ZDT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Zhen Ding Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>4</v>
@@ -16771,17 +17975,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -16797,24 +18001,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
         <v>1</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
@@ -16823,24 +18027,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -16849,24 +18053,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -16875,17 +18079,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -16901,102 +18105,102 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -17005,24 +18209,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -17031,17 +18235,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -17057,17 +18261,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -17083,24 +18287,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -17109,12 +18313,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17123,10 +18327,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -17135,24 +18339,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -17161,24 +18365,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -17187,24 +18391,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
         <v>3</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -17213,12 +18417,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17239,24 +18443,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -17265,24 +18469,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -17291,24 +18495,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -17317,17 +18521,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -17343,17 +18547,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -17369,24 +18573,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SpaceX (Colossus compute)</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -17395,38 +18599,38 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -17435,133 +18639,133 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>SpaceX (Colossus compute)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>CAMBRICON</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>Cambricon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -17577,17 +18781,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -17603,17 +18807,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -17629,17 +18833,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -17655,17 +18859,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -17681,17 +18885,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -17707,17 +18911,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -17733,17 +18937,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -17759,17 +18963,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -17785,24 +18989,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -17811,24 +19015,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -17837,17 +19041,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -17863,17 +19067,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -17889,17 +19093,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NANYA</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -17915,12 +19119,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -17941,90 +19145,90 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
         <v>0</v>
       </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -18033,29 +19237,29 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -18071,24 +19275,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
         <v>1</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -18097,24 +19301,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
         <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -18123,24 +19327,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
         <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -18149,17 +19353,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -18175,17 +19379,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -18201,12 +19405,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18227,17 +19431,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cipher Mining</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -18253,24 +19457,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>XLIGHT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>XLight</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
         <v>0</v>
-      </c>
-      <c r="E95" t="n">
-        <v>1</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -18279,17 +19483,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -18305,17 +19509,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SAMBANOVA</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Cipher Mining</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -18331,17 +19535,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BYTEDANCE</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -18351,6 +19555,162 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Entegris</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SAMBANOVA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>BYTEDANCE</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>LARGAN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Largan Precision</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WIWYNN</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Wiwynn</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CAMT</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Camtek</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -5762,6 +5762,352 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Naver</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>035420.KS</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>Cloud / sovereign AI</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>DSX AI datacenters, Korean cloud/search</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
+        <is>
+          <t>Korean internet giant building sovereign-AI infra on NVIDIA DSX</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>DOOSAN</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Doosan</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>000150.KS</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>Power &amp; cooling</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>Power systems, datacenter infrastructure</t>
+        </is>
+      </c>
+      <c r="J106" s="8" t="inlineStr">
+        <is>
+          <t>Korean industrial partner in NVIDIA Korea AI buildout</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>HITACHI</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Hitachi</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>6501.T</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>process/etch tools, edge-AI &amp; digital-infra systems</t>
+        </is>
+      </c>
+      <c r="J107" s="8" t="inlineStr">
+        <is>
+          <t>Foundry-tool &amp; custom-silicon collaboration partner to Intel</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>Consumer AI / cloud compute</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>Apple Intelligence, Private Cloud Compute, Apple silicon, Foundation Models</t>
+        </is>
+      </c>
+      <c r="J108" s="8" t="inlineStr">
+        <is>
+          <t>Large AI compute buyer; runs Private Cloud Compute on Google Cloud Nvidia GPUs</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>CBRS</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>CBRS</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>Wafer-scale AI accelerators</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>Wafer-Scale Engine (WSE), fast inference cloud</t>
+        </is>
+      </c>
+      <c r="J109" s="8" t="inlineStr">
+        <is>
+          <t>Wafer-scale inference accelerator; low-latency inference challenger to NVIDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>KIOXIA</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Kioxia Holdings</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>Memory (NAND)</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>BiCS NAND flash, enterprise/datacenter SSDs</t>
+        </is>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
+        <is>
+          <t>NAND flash &amp; SSD supplier for AI inference/storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>ALLSPACE</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>ALL.SPACE</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr"/>
+      <c r="E111" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Networking Systems</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>SATCOM terminals / multi-orbit antennas</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>Ka-band multi-orbit satellite communication terminals</t>
+        </is>
+      </c>
+      <c r="J111" s="8" t="inlineStr">
+        <is>
+          <t>End customer for Sivers beamforming ICs in defense/commercial SATCOM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5776,7 +6122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I258"/>
+  <dimension ref="A1:I272"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -16721,6 +17067,636 @@
       <c r="I258" s="8" t="inlineStr">
         <is>
           <t>CITI-Zhen Ding Technology （4958.TW） Optical module and substrate on the rise； upgrade to Buy-260605.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>SKHYNIX</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>SK Hynix</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D259" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E259" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F259" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G259" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-08): NVIDIA–SK Hynix multiyear partnership co-developing SOCAMM2/HBM4 for Vera Rubin; applies CUDA-X, PhysicsNeMo, Omniverse to SK Hynix chip design, TCAD and autonomous fab digital twins</t>
+        </is>
+      </c>
+      <c r="H259" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I259" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-07-2003-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B260" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C260" s="8" t="inlineStr">
+        <is>
+          <t>sells GPUs to</t>
+        </is>
+      </c>
+      <c r="D260" s="8" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="E260" s="8" t="inlineStr">
+        <is>
+          <t>Naver</t>
+        </is>
+      </c>
+      <c r="F260" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G260" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-08): Naver to build sovereign-AI datacenters on NVIDIA DSX platform, 55MW starting scaling to GW-scale</t>
+        </is>
+      </c>
+      <c r="H260" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I260" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-08-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="inlineStr">
+        <is>
+          <t>DOOSAN</t>
+        </is>
+      </c>
+      <c r="E261" s="8" t="inlineStr">
+        <is>
+          <t>Doosan</t>
+        </is>
+      </c>
+      <c r="F261" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-08): NVIDIA announced AI-infrastructure partnership with Doosan during Korea trip</t>
+        </is>
+      </c>
+      <c r="H261" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I261" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-08-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="8" t="inlineStr">
+        <is>
+          <t>HITACHI</t>
+        </is>
+      </c>
+      <c r="B262" s="8" t="inlineStr">
+        <is>
+          <t>Hitachi</t>
+        </is>
+      </c>
+      <c r="C262" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D262" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E262" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F262" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G262" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-08): Intel &amp; Hitachi strategic collaboration on foundry tools, custom silicon, quantum, energy optimization &amp; edge-AI ("physical AI").</t>
+        </is>
+      </c>
+      <c r="H262" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I262" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-08-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>sells GPUs to</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E263" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F263" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G263" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-08): Apple Private Cloud Compute runs on Nvidia GPUs (NVIDIA Confidential Computing) via Google Cloud.</t>
+        </is>
+      </c>
+      <c r="H263" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I263" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-08-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="8" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B264" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C264" s="8" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D264" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E264" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F264" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G264" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-08): Apple expanded Private Cloud Compute to Google Cloud infrastructure for Apple Intelligence workloads.</t>
+        </is>
+      </c>
+      <c r="H264" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I264" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-08-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="8" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E265" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F265" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G265" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-08): Apple uses Gemini-family model technology to build next-gen Apple Foundation Models.</t>
+        </is>
+      </c>
+      <c r="H265" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I265" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-08-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="8" t="inlineStr">
+        <is>
+          <t>CBRS</t>
+        </is>
+      </c>
+      <c r="B266" s="8" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C266" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D266" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E266" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F266" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G266" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-08): wafer-scale low-latency inference; contracts point to $6bn 2028 rev / ~1% AI processor share; Initiate OW, PT $250.</t>
+        </is>
+      </c>
+      <c r="H266" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I266" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Cerebras Systems Initiate at OW-260608.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>CBRS</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>competes with</t>
+        </is>
+      </c>
+      <c r="D267" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E267" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F267" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G267" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-08): competes in AI inference processors; key risk is competition incl. NVIDIA.</t>
+        </is>
+      </c>
+      <c r="H267" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I267" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-Cerebras Systems Initiate at OW-260608.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="8" t="inlineStr">
+        <is>
+          <t>KIOXIA</t>
+        </is>
+      </c>
+      <c r="B268" s="8" t="inlineStr">
+        <is>
+          <t>Kioxia Holdings</t>
+        </is>
+      </c>
+      <c r="C268" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D268" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E268" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F268" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G268" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-08): NAND/SSD (CM/GP/LC series) for diverse AI inference; tight NAND supply, ~50% CY28 volume under LTA; reiterate OW.</t>
+        </is>
+      </c>
+      <c r="H268" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I268" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley-KIOXIA Holdings Group Call-260608.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>supplies optical fiber to</t>
+        </is>
+      </c>
+      <c r="D269" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="E269" s="8" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F269" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G269" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, TMTB 2026-06-08): Corning struck deal to supply optical fiber for Amazon US AI data centers.</t>
+        </is>
+      </c>
+      <c r="H269" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I269" s="8" t="inlineStr">
+        <is>
+          <t>TMTB EOD Wrap 2026-06-08.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="8" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B270" s="8" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="C270" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D270" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E270" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F270" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G270" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, TMTB 2026-06-08): optical fiber demand scaling with AI datacenter buildout.</t>
+        </is>
+      </c>
+      <c r="H270" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I270" s="8" t="inlineStr">
+        <is>
+          <t>TMTB EOD Wrap 2026-06-08.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>Supermicro</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>builds AI servers for</t>
+        </is>
+      </c>
+      <c r="D271" s="8" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="E271" s="8" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="F271" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G271" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, TMTB/Bluefin via X 2026-06-08): reported award of 1,500 racks (~$5B+) from xAI (?).</t>
+        </is>
+      </c>
+      <c r="H271" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I271" s="8" t="inlineStr">
+        <is>
+          <t>TMTB EOD Wrap 2026-06-08.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="8" t="inlineStr">
+        <is>
+          <t>SIVE</t>
+        </is>
+      </c>
+      <c r="B272" s="8" t="inlineStr">
+        <is>
+          <t>Sivers Semiconductor</t>
+        </is>
+      </c>
+      <c r="C272" s="8" t="inlineStr">
+        <is>
+          <t>supplies beamforming ICs to</t>
+        </is>
+      </c>
+      <c r="D272" s="8" t="inlineStr">
+        <is>
+          <t>ALLSPACE</t>
+        </is>
+      </c>
+      <c r="E272" s="8" t="inlineStr">
+        <is>
+          <t>ALL.SPACE</t>
+        </is>
+      </c>
+      <c r="F272" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G272" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-09): ALL.SPACE awarded Sivers an $8.2M production order for 2027 Ka-band multi-beam BFICs for multi-orbit satellite comms</t>
+        </is>
+      </c>
+      <c r="H272" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I272" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-09-0404-x-scan.md</t>
         </is>
       </c>
     </row>
@@ -17001,7 +17977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17053,24 +18029,24 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T_CPO</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Co-Packaged Optics (CPO)</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -17091,50 +18067,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>T_CPO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Co-Packaged Optics (CPO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>20</v>
@@ -17160,10 +18136,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -17290,59 +18266,59 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Alphabet (Google)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alphabet (Google)</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
@@ -17368,10 +18344,10 @@
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -17533,24 +18509,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -17559,12 +18535,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -17585,24 +18561,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
@@ -17611,24 +18587,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -17637,24 +18613,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T_GLASS</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Glass Core Substrate</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
         <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>6</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
@@ -17663,24 +18639,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>T_GLASS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Glass Core Substrate</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
@@ -17689,38 +18665,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17729,10 +18705,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -17741,24 +18717,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -17767,17 +18743,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -17897,24 +18873,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -17923,24 +18899,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ZDT</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zhen Ding Technology</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -17949,38 +18925,38 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>ZDT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Zhen Ding Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -18001,24 +18977,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
@@ -18027,24 +19003,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -18053,24 +19029,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
         <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>3</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -18079,17 +19055,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -18105,24 +19081,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
@@ -18131,24 +19107,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -18157,24 +19133,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -18183,69 +19159,69 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -18261,24 +19237,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -18287,24 +19263,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -18313,24 +19289,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -18339,12 +19315,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -18365,12 +19341,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18379,10 +19355,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -18391,24 +19367,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
         <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>3</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -18417,24 +19393,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -18443,12 +19419,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -18457,10 +19433,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -18573,24 +19549,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -18599,24 +19575,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -18625,12 +19601,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18639,10 +19615,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -18651,12 +19627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18677,24 +19653,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SpaceX (Colossus compute)</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
         <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -18703,24 +19679,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>SpaceX (Colossus compute)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
         <v>3</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -18729,24 +19705,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CAMBRICON</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cambricon</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -18755,64 +19731,64 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CAMBRICON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Cambricon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18833,17 +19809,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -18859,17 +19835,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -18885,17 +19861,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -18911,17 +19887,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -18937,17 +19913,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -18963,17 +19939,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -18989,24 +19965,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
         <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>2</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -19015,17 +19991,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -19041,24 +20017,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -19067,17 +20043,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -19093,17 +20069,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -19119,17 +20095,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -19145,17 +20121,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -19171,24 +20147,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -19197,24 +20173,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NANYA</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -19223,24 +20199,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -19249,95 +20225,95 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
         <v>0</v>
       </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -19353,24 +20329,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
         <v>1</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -19379,24 +20355,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
         <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -19405,17 +20381,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -19431,17 +20407,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -19457,17 +20433,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -19483,12 +20459,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -19509,17 +20485,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cipher Mining</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -19535,24 +20511,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>XLIGHT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>XLight</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
         <v>0</v>
-      </c>
-      <c r="E98" t="n">
-        <v>1</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
@@ -19561,17 +20537,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -19587,17 +20563,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SAMBANOVA</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Cipher Mining</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -19613,24 +20589,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BYTEDANCE</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
         <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>1</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -19639,17 +20615,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LARGAN</t>
+          <t>SAMBANOVA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Largan Precision</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -19665,24 +20641,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>WIWYNN</t>
+          <t>BYTEDANCE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wiwynn</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
         <v>1</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -19691,17 +20667,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>LARGAN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Camtek</t>
+          <t>Largan Precision</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -19711,6 +20687,188 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WIWYNN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wiwynn</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CAMT</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Camtek</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Naver</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DOOSAN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Doosan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>HITACHI</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hitachi</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KIOXIA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Kioxia Holdings</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ALLSPACE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ALL.SPACE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Networking Systems</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -6108,6 +6108,156 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>HANMI</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Hanmi Semiconductor</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>042700.KQ</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>Advanced packaging / HBM bonding tools</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>TC bonders (TC Bonder 4.5 Griffin), HBM die-stacking equipment</t>
+        </is>
+      </c>
+      <c r="J112" s="8" t="inlineStr">
+        <is>
+          <t>Supplies thermal-compression bonders to memory makers for HBM4 stacking</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Amphenol</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>Connectors / copper interconnect</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>High-speed connectors, copper cable assemblies for AI racks</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t>Copper interconnect supplier for AI scale-up networks; beneficiary if CPO is delayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>FormFactor</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>Test &amp; measurement (probe cards)</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>Probe cards, PIC wafer probing for optical engines</t>
+        </is>
+      </c>
+      <c r="J114" s="8" t="inlineStr">
+        <is>
+          <t>CPO test picks-and-shovels; PIC wafer probing ahead of CPO volume</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -6122,7 +6272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I272"/>
+  <dimension ref="A1:I279"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -10349,7 +10499,11 @@
       <c r="F103" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G103" s="15" t="n"/>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, SemiAnalysis 2026-06-09): 800VDC pushout to 2028+ neutral-to-positive for VRT — extends life of large UPS business; grey-space power rack demoed at Computex</t>
+        </is>
+      </c>
       <c r="H103" s="15" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -10991,7 +11145,7 @@
       </c>
       <c r="G119" s="16" t="inlineStr">
         <is>
-          <t>(VIEW, Nomura) optics shift to CPO/LPO</t>
+          <t>(VIEW, Nomura) optics shift to CPO/LPO; (FACT, X-scan 2026-06-09): incremental multi-hundred-$M CPO order tied to NVDA Spectrum-X/Quantum-X (Mizuho 6/9); (VIEW, SemiAnalysis 2026-06-09): cautious on timing — scale-out CPO shipments to be revised down, scale-up CPO volume ramp ~2029</t>
         </is>
       </c>
       <c r="H119" s="16" t="inlineStr">
@@ -17697,6 +17851,321 @@
       <c r="I272" s="8" t="inlineStr">
         <is>
           <t>X-Reports/2026-06-09-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>HUAWEI</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="inlineStr">
+        <is>
+          <t>T_CHINA</t>
+        </is>
+      </c>
+      <c r="E273" s="8" t="inlineStr">
+        <is>
+          <t>China Indigenous AI Buildout</t>
+        </is>
+      </c>
+      <c r="F273" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G273" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-09): Bloomberg — China prepping ~$295B (¥2T) nationwide AI-datacenter buildout, &gt;=80% domestic tech incl. Huawei chips</t>
+        </is>
+      </c>
+      <c r="H273" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I273" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-09-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="8" t="inlineStr">
+        <is>
+          <t>HANMI</t>
+        </is>
+      </c>
+      <c r="B274" s="8" t="inlineStr">
+        <is>
+          <t>Hanmi Semiconductor</t>
+        </is>
+      </c>
+      <c r="C274" s="8" t="inlineStr">
+        <is>
+          <t>supplies HBM bonding equipment to</t>
+        </is>
+      </c>
+      <c r="D274" s="8" t="inlineStr">
+        <is>
+          <t>SKHYNIX</t>
+        </is>
+      </c>
+      <c r="E274" s="8" t="inlineStr">
+        <is>
+          <t>SK Hynix</t>
+        </is>
+      </c>
+      <c r="F274" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G274" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-09): SK Hynix placed W44.2B (~15 units) order for TC Bonder 4.5 Griffin to ramp HBM4 (TrendForce/Korea Herald 6/9)</t>
+        </is>
+      </c>
+      <c r="H274" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I274" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-09-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D275" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E275" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F275" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G275" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-09): Apple Private Cloud Compute runs Apple Intelligence on NVIDIA GPUs via Google Cloud (announced 6/9)</t>
+        </is>
+      </c>
+      <c r="H275" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I275" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-09-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="8" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B276" s="8" t="inlineStr">
+        <is>
+          <t>Supermicro</t>
+        </is>
+      </c>
+      <c r="C276" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D276" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E276" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F276" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G276" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-09): Supermicro disclosed ~$39B AI-server orders from &gt;20 customers, raising $7B to fund components</t>
+        </is>
+      </c>
+      <c r="H276" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I276" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-09-2004-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
+        <is>
+          <t>Amphenol</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D277" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E277" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F277" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G277" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, SemiAnalysis 2026-06-09): CPO delays keep copper primary for scale-up; most positive on copper names (APH/SMTC/MTSI); copper TAM seen ~3x in next few years</t>
+        </is>
+      </c>
+      <c r="H277" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I277" s="8" t="inlineStr">
+        <is>
+          <t>Semianalysis 原文- Powered Down, Lights Off. 800VDC Pushout and CPO Delays.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="8" t="inlineStr">
+        <is>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="B278" s="8" t="inlineStr">
+        <is>
+          <t>FormFactor</t>
+        </is>
+      </c>
+      <c r="C278" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D278" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E278" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F278" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G278" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, SemiAnalysis 2026-06-09): CPO test is picks-and-shovels beneficiary ahead of CPO volume; FormFactor for PIC wafer probing</t>
+        </is>
+      </c>
+      <c r="H278" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I278" s="8" t="inlineStr">
+        <is>
+          <t>Semianalysis 原文- Powered Down, Lights Off. 800VDC Pushout and CPO Delays.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
+        <is>
+          <t>Teradyne</t>
+        </is>
+      </c>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D279" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E279" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F279" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G279" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, SemiAnalysis 2026-06-09): frontrunner in NVIDIA CPO test qualification; ficonTEC partnership</t>
+        </is>
+      </c>
+      <c r="H279" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I279" s="8" t="inlineStr">
+        <is>
+          <t>Semianalysis 原文- Powered Down, Lights Off. 800VDC Pushout and CPO Delays.pdf</t>
         </is>
       </c>
     </row>
@@ -17977,7 +18446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18032,21 +18501,21 @@
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>T_CPO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>Co-Packaged Optics (CPO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18058,21 +18527,21 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T_CPO</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Co-Packaged Optics (CPO)</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18084,59 +18553,59 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>T_INFER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>AI Inference Demand</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T_INFER</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AI Inference Demand</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
@@ -18353,12 +18822,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T_HBM</t>
+          <t>T_CHINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HBM Demand</t>
+          <t>China Indigenous AI Buildout</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -18370,21 +18839,21 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T_CHINA</t>
+          <t>T_HBM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>China Indigenous AI Buildout</t>
+          <t>HBM Demand</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -18483,50 +18952,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -18691,24 +19160,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -18717,12 +19186,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -18731,10 +19200,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -18743,24 +19212,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -18769,24 +19238,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -18795,24 +19264,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -18821,24 +19290,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -18847,24 +19316,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -18873,24 +19342,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -18899,24 +19368,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -18925,24 +19394,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ZDT</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zhen Ding Technology</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -18951,38 +19420,38 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>ZDT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Zhen Ding Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -19003,24 +19472,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -19029,17 +19498,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -19211,43 +19680,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -19263,24 +19732,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -19289,24 +19758,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -19315,24 +19784,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -19341,12 +19810,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -19367,12 +19836,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -19381,10 +19850,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -19393,24 +19862,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
         <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -19419,24 +19888,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -19445,12 +19914,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -19471,17 +19940,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -19497,24 +19966,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -19523,24 +19992,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -19549,17 +20018,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -19575,24 +20044,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -19601,12 +20070,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -19615,10 +20084,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -19627,24 +20096,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -19653,12 +20122,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19667,10 +20136,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -19679,24 +20148,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SpaceX (Colossus compute)</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
         <v>0</v>
-      </c>
-      <c r="E66" t="n">
-        <v>3</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -19705,17 +20174,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -19731,24 +20200,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CAMBRICON</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cambricon</t>
+          <t>SpaceX (Colossus compute)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -19757,24 +20226,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -19783,43 +20252,43 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CAMBRICON</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Cambricon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -19835,17 +20304,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -19861,12 +20330,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19887,17 +20356,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -19913,17 +20382,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -19939,17 +20408,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -19965,17 +20434,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -19991,17 +20460,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -20017,24 +20486,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="n">
         <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -20043,17 +20512,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -20069,12 +20538,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -20095,17 +20564,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -20121,17 +20590,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -20147,17 +20616,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -20173,24 +20642,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -20199,24 +20668,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -20225,24 +20694,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NANYA</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -20251,17 +20720,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -20277,17 +20746,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -20303,50 +20772,50 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
         <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -20355,17 +20824,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -20381,24 +20850,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
         <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -20407,17 +20876,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -20433,12 +20902,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -20459,17 +20928,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -20485,17 +20954,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -20869,6 +21338,84 @@
         <v>1</v>
       </c>
       <c r="F111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>HANMI</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Hanmi Semiconductor</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Amphenol</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FormFactor</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -6258,6 +6258,156 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>Optical networking systems</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>Coherent optical transport (WaveLogic), DCI systems</t>
+        </is>
+      </c>
+      <c r="J115" s="8" t="inlineStr">
+        <is>
+          <t>Optical transport/DCI for hyperscaler AI interconnect</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>IFX</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>IFX.DE</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>Power semiconductors (Si/SiC/GaN)</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>Superjunction MOSFETs, SiC/GaN power devices for DC power shelves/VRMs</t>
+        </is>
+      </c>
+      <c r="J116" s="8" t="inlineStr">
+        <is>
+          <t>Power-semi supplier to AI datacenter power chain; hedged across Si/SiC/GaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>EMS / datacenter power (Anord Mardix)</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>USA/Singapore</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>AI server assembly, embedded &amp; critical power products</t>
+        </is>
+      </c>
+      <c r="J117" s="8" t="inlineStr">
+        <is>
+          <t>EMS + turnkey DC power infrastructure for AI buildout</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -6272,7 +6422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I279"/>
+  <dimension ref="A1:I286"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -18166,6 +18316,321 @@
       <c r="I279" s="8" t="inlineStr">
         <is>
           <t>Semianalysis 原文- Powered Down, Lights Off. 800VDC Pushout and CPO Delays.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="8" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="B280" s="8" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D280" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E280" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F280" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G280" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, BofA 2026-06-10): upgraded to Buy — earnings inflection driven by AI optical interconnects, LEO satellites; earnings power underappreciated</t>
+        </is>
+      </c>
+      <c r="H280" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I280" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="8" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D281" s="8" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E281" s="8" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F281" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G281" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; industry fundamentals already at levels previously expected for 2028</t>
+        </is>
+      </c>
+      <c r="H281" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I281" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="8" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B282" s="8" t="inlineStr">
+        <is>
+          <t>Lam Research</t>
+        </is>
+      </c>
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D282" s="8" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E282" s="8" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F282" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G282" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; fundamentals at levels previously expected for 2028</t>
+        </is>
+      </c>
+      <c r="H282" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I282" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="inlineStr">
+        <is>
+          <t>KLA Corporation</t>
+        </is>
+      </c>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D283" s="8" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E283" s="8" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F283" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G283" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; fundamentals at levels previously expected for 2028</t>
+        </is>
+      </c>
+      <c r="H283" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I283" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="8" t="inlineStr">
+        <is>
+          <t>IFX</t>
+        </is>
+      </c>
+      <c r="B284" s="8" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+      <c r="C284" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D284" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E284" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F284" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G284" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Jefferies 2026-06-10): 800V pushout neutral/positive for IFX; corroborates (VIEW, SemiAnalysis 2026-06-09) that Infineon is best-positioned power semi, hedged across Si superjunction/SiC/GaN</t>
+        </is>
+      </c>
+      <c r="H284" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I284" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="8" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E285" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F285" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G285" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06-10): key beneficiary of AI datacenter power-architecture evolution; turnkey power infrastructure and 800V adoption</t>
+        </is>
+      </c>
+      <c r="H285" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I285" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="8" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="B286" s="8" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D286" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E286" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F286" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G286" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06-10): improving order visibility, accelerating SP spend, AI networking on hyperscaler demand for advanced optical</t>
+        </is>
+      </c>
+      <c r="H286" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I286" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
         </is>
       </c>
     </row>
@@ -18446,7 +18911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18510,12 +18975,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T_CPO</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Co-Packaged Optics (CPO)</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18527,21 +18992,21 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>T_CPO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>Co-Packaged Optics (CPO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18553,10 +19018,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -18614,102 +19079,102 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>T_TRAIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>AI Training Capex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>T_POWER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Datacenter Power Demand</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T_TRAIN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AI Training Capex</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T_POWER</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Datacenter Power Demand</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>14</v>
@@ -19498,24 +19963,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -19524,24 +19989,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>4</v>
@@ -19550,24 +20015,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
@@ -19576,24 +20041,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -19602,24 +20067,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -19628,17 +20093,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -19654,24 +20119,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -19680,24 +20145,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -19706,76 +20171,76 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -19784,17 +20249,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -19810,17 +20275,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -19836,24 +20301,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -19862,12 +20327,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -19876,10 +20341,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -19888,24 +20353,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -19914,24 +20379,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -19940,24 +20405,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -19966,24 +20431,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
         <v>1</v>
-      </c>
-      <c r="E59" t="n">
-        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -19992,17 +20457,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -20018,24 +20483,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -20044,24 +20509,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -20070,17 +20535,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -20096,24 +20561,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -20122,12 +20587,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -20136,10 +20601,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -20148,24 +20613,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -20174,12 +20639,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -20188,10 +20653,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -20200,24 +20665,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SpaceX (Colossus compute)</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
         <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>3</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -20226,24 +20691,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>SpaceX (Colossus compute)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
         <v>3</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -20252,24 +20717,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CAMBRICON</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cambricon</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -20278,43 +20743,43 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CAMBRICON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Cambricon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -20330,17 +20795,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -20356,12 +20821,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -20382,17 +20847,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -20408,17 +20873,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -20434,17 +20899,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -20460,17 +20925,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -20486,17 +20951,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -20512,17 +20977,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -20538,17 +21003,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -20564,12 +21029,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -20590,17 +21055,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -20616,17 +21081,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -20642,17 +21107,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -20668,24 +21133,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -20694,24 +21159,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -20720,24 +21185,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NANYA</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
@@ -20746,17 +21211,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -20772,17 +21237,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -20798,27 +21263,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -21416,6 +21881,84 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ciena</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IFX</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -6408,6 +6408,606 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>ENR</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>ENR1n.DE</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>Power Generation / Utilities</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>Power equipment</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>Gas turbines, grid technology, transformers</t>
+        </is>
+      </c>
+      <c r="J118" s="8" t="inlineStr">
+        <is>
+          <t>Big-3 gas-turbine maker (with GEV, MHI) supplying datacenter prime power and grid equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>DELTA</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>Delta Electronics</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>2308.TW</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>Power supplies &amp; thermal</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>Server power supplies, 800VDC power racks, cooling</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t>Leading AI-server power vendor; first expected to mass-produce 800VDC standalone power racks</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>SINOCERA</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Sinocera</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>300285.SZ</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>Electronic ceramic materials</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>MLCC ceramic powders (consumer/auto/AI-server grade), ceramic substrates</t>
+        </is>
+      </c>
+      <c r="J120" s="8" t="inlineStr">
+        <is>
+          <t>Dominant MLCC powder supplier (&gt;80% China, ~20% global) feeding AI-server MLCC chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>ASE</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>ASE Technology</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>3711.TW</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>Advanced packaging, test, CPO assembly</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
+        <is>
+          <t>World's largest OSAT; key co-packaged-optics assembly enabler</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>3363.TWO</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>Fiber-optic connectors</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>Fiber array units, CPO connector/external-laser components</t>
+        </is>
+      </c>
+      <c r="J122" s="8" t="inlineStr">
+        <is>
+          <t>CPO connectivity component maker; CPO revenue ramp expected from late 3Q26</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>Storage (HDD/NAND)</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>Nearline HDDs; enterprise storage</t>
+        </is>
+      </c>
+      <c r="J123" s="8" t="inlineStr">
+        <is>
+          <t>HDD supplier to hyperscalers; levered to AI data-storage demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Seagate Technology</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>Storage (HDD)</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>Nearline HDDs (HAMR)</t>
+        </is>
+      </c>
+      <c r="J124" s="8" t="inlineStr">
+        <is>
+          <t>HDD supplier to hyperscalers; levered to AI data-storage demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>WOLF</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>Wolfspeed</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>WOLF</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>Power semiconductors (SiC)</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>SiC devices &amp; substrates</t>
+        </is>
+      </c>
+      <c r="J125" s="8" t="inlineStr">
+        <is>
+          <t>SiC power devices levered to 800VDC datacenter power architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Navitas Semiconductor</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>Power semiconductors (GaN/SiC)</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>GaN/SiC power ICs</t>
+        </is>
+      </c>
+      <c r="J126" s="8" t="inlineStr">
+        <is>
+          <t>GaN/SiC power devices levered to 800VDC datacenter power architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>AI chips / robotics / energy</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>Dojo/AI chips; Optimus; energy storage</t>
+        </is>
+      </c>
+      <c r="J127" s="8" t="inlineStr">
+        <is>
+          <t>Terafab chip-manufacturing JV partner with SpaceX and Intel</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>INNOLIGHT</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Zhongji Innolight</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>300308.SZ</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>Optical transceivers</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>800G/1.6T optical transceivers; NPO</t>
+        </is>
+      </c>
+      <c r="J128" s="8" t="inlineStr">
+        <is>
+          <t>Leading optical transceiver maker, &gt;40% global 1.6T share; key Google supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>Tower Semiconductor</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>Foundry / Manufacturing</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>Specialty foundry (SiPho)</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t>Silicon photonics foundry (PICs)</t>
+        </is>
+      </c>
+      <c r="J129" s="8" t="inlineStr">
+        <is>
+          <t>SiPho foundry supplying the optical transceiver chain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -6422,7 +7022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I286"/>
+  <dimension ref="A1:I310"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -10259,7 +10859,11 @@
       <c r="F93" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G93" s="15" t="n"/>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>None | (FACT, X-scan 2026-06-11): entire 2026 HBM capacity booked/sold out under binding contracts; HBM4 stack shown at COMPUTEX 2026</t>
+        </is>
+      </c>
       <c r="H93" s="15" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -10838,7 +11442,11 @@
       <c r="F108" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G108" s="15" t="n"/>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>None | (FACT, BofA 2026-06-10): capacity fully booked through 2028</t>
+        </is>
+      </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -16595,7 +17203,7 @@
       </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
-          <t>(FACT, Citi 2026-06): COUPE packaging + chip testing for CPO</t>
+          <t>(FACT, Citi 2026-06): COUPE packaging + chip testing for CPO | (FACT, Morgan Stanley 2026-06-10): TSMC to expand PIC capacity to 10kwpm in 1Q27; SoIC yield 50-60% remains swing factor</t>
         </is>
       </c>
       <c r="H241" s="8" t="inlineStr">
@@ -18631,6 +19239,1086 @@
       <c r="I286" s="8" t="inlineStr">
         <is>
           <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>ENR</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E287" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F287" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G287" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-09): Big-3 turbine makers (GEV/ENR/MHI) ~74% of traditional gas-turbine supply; MS raised 2030 gas-turbine/DC prime-power supply model to 135GW on datacenter demand, flags post-2030 oversupply risk</t>
+        </is>
+      </c>
+      <c r="H287" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I287" s="8" t="inlineStr">
+        <is>
+          <t>20260609-Morgan Stanley-Siemens Energy AG （ENR1n.DE）Caught in multiple crosswinds. Supply_demand dyn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="8" t="inlineStr">
+        <is>
+          <t>DELTA</t>
+        </is>
+      </c>
+      <c r="B288" s="8" t="inlineStr">
+        <is>
+          <t>Delta Electronics</t>
+        </is>
+      </c>
+      <c r="C288" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D288" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E288" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F288" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G288" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-10): Delta likely first vendor to mass-produce 800VDC standalone power racks in 4Q26 for a major US hyperscaler; 800VDC schedule intact per Computex checks (NVDA denied SemiAnalysis delay report; 800VDC rack MP 3Q26)</t>
+        </is>
+      </c>
+      <c r="H288" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I288" s="8" t="inlineStr">
+        <is>
+          <t>大摩关于 800V.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>SINOCERA</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>Sinocera</t>
+        </is>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D289" s="8" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E289" s="8" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F289" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G289" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, J.P. Morgan fireside 2026-06-10): AI-server demand drove high-end MLCC powder upcycle in 1H26; AI server-grade powder &gt;Rmb100k/t at 45-50% GM; 20%+ FY26 revenue growth target</t>
+        </is>
+      </c>
+      <c r="H289" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I289" s="8" t="inlineStr">
+        <is>
+          <t>J.P. Morgan-MLCC Powder：Growth empowered by high~end MLCC demand： 10 key takeaways from fireside chat with Sinocera-260610.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="8" t="inlineStr">
+        <is>
+          <t>SINOCERA</t>
+        </is>
+      </c>
+      <c r="B290" s="8" t="inlineStr">
+        <is>
+          <t>Sinocera</t>
+        </is>
+      </c>
+      <c r="C290" s="8" t="inlineStr">
+        <is>
+          <t>supplies MLCC powder to</t>
+        </is>
+      </c>
+      <c r="D290" s="8" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="E290" s="8" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="F290" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G290" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, J.P. Morgan 2026-06-10): AI/automotive-grade MLCC powder completed qualification at Samsung (core international high-end customer — Samsung group component arm, likely Samsung Electro-Mechanics) (?); volume shipments from 3Q26</t>
+        </is>
+      </c>
+      <c r="H290" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I290" s="8" t="inlineStr">
+        <is>
+          <t>J.P. Morgan-MLCC Powder：Growth empowered by high~end MLCC demand： 10 key takeaways from fireside chat with Sinocera-260610.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>ASE</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
+        <is>
+          <t>ASE Technology</t>
+        </is>
+      </c>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D291" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E291" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F291" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G291" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-10): named key CPO enabler (OW); MS models 2027 optical-engine shipments 6-7mn units vs investor expectations of 20-30mn; CPO boom from 2028 onward</t>
+        </is>
+      </c>
+      <c r="H291" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I291" s="8" t="inlineStr">
+        <is>
+          <t>大摩关于 CPO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="8" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="B292" s="8" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="C292" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D292" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E292" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F292" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G292" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-10): key CPO enabler (OW); CPO revenue should start to ramp late 3Q26 ahead of 2028 CPO inflection</t>
+        </is>
+      </c>
+      <c r="H292" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I292" s="8" t="inlineStr">
+        <is>
+          <t>大摩关于 CPO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C293" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D293" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E293" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F293" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G293" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Citi 2026-06-10): F4Q26 RPO $638B (+363% y/y) led by large prepaid AI contracts; OCI revenue +92% y/y cc; FY27 $90B revenue target reiterated</t>
+        </is>
+      </c>
+      <c r="H293" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I293" s="8" t="inlineStr">
+        <is>
+          <t>甲骨文业绩.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="8" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B294" s="8" t="inlineStr">
+        <is>
+          <t>Bloom Energy</t>
+        </is>
+      </c>
+      <c r="C294" s="8" t="inlineStr">
+        <is>
+          <t>supplies on-site fuel-cell power to</t>
+        </is>
+      </c>
+      <c r="D294" s="8" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="E294" s="8" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="F294" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G294" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Jefferies 2026-06-08): expanded Oracle–Bloom Energy partnership adds faster on-site fuel-cell power that bypasses grid constraints for OCI AI buildout</t>
+        </is>
+      </c>
+      <c r="H294" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I294" s="8" t="inlineStr">
+        <is>
+          <t>Jefferies-Oracle （ORCL.US）：Positive on Leadership Add， Mixed on Capex Needs-260608.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C295" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D295" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E295" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F295" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G295" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06-11): HDD pricing accelerating faster than expected on AI demand; LTAs support durable pricing and margin expansion</t>
+        </is>
+      </c>
+      <c r="H295" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I295" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="8" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B296" s="8" t="inlineStr">
+        <is>
+          <t>Seagate Technology</t>
+        </is>
+      </c>
+      <c r="C296" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D296" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E296" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F296" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G296" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06-11): HDD pricing accelerating faster than expected on AI demand; LTAs support durable pricing and margin expansion</t>
+        </is>
+      </c>
+      <c r="H296" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I296" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C297" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D297" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E297" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F297" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G297" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, BofA 2026-06-11): double-upgrade to Buy ($135 PO); agentic AI expands CY30 server CPU TAM to $170bn+, INTC server CPU sales ~$40bn+ (~25% share) potential</t>
+        </is>
+      </c>
+      <c r="H297" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I297" s="8" t="inlineStr">
+        <is>
+          <t>CPU.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C298" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D298" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E298" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F298" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G298" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, BofA 2026-06-11): agentic AI lifts ARM challengers within $170bn+ CY30 server CPU TAM; PO raised to $335 on chiplet potential</t>
+        </is>
+      </c>
+      <c r="H298" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I298" s="8" t="inlineStr">
+        <is>
+          <t>CPU.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="8" t="inlineStr">
+        <is>
+          <t>WOLF</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
+        <is>
+          <t>Wolfspeed</t>
+        </is>
+      </c>
+      <c r="C299" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D299" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E299" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F299" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, SemiAnalysis via TMTB 2026-06-10): 800VDC is where SiC content inflects; pushout talk to 2028+ removes near-term catalyst (?)</t>
+        </is>
+      </c>
+      <c r="H299" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I299" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="8" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B300" s="8" t="inlineStr">
+        <is>
+          <t>Navitas Semiconductor</t>
+        </is>
+      </c>
+      <c r="C300" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D300" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E300" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F300" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, SemiAnalysis via TMTB 2026-06-10): 800VDC is where GaN content inflects; pushout talk to 2028+ removes near-term catalyst (?)</t>
+        </is>
+      </c>
+      <c r="H300" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I300" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="8" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="E301" s="8" t="inlineStr">
+        <is>
+          <t>Blackstone</t>
+        </is>
+      </c>
+      <c r="F301" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G301" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-11): Broadcom + Apollo + Blackstone launched strategic platform (June 9 2026) to accelerate 20GW+ of global AI datacenter deployments</t>
+        </is>
+      </c>
+      <c r="H301" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I301" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-11-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B302" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="C302" s="8" t="inlineStr">
+        <is>
+          <t>acquired</t>
+        </is>
+      </c>
+      <c r="D302" s="8" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="E302" s="8" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="F302" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G302" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Oppenheimer 2026-06-11): SpaceX acquired xAI early 2026 for $250B (incl. X, Grok, Colossus, Macrohard)</t>
+        </is>
+      </c>
+      <c r="H302" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I302" s="8" t="inlineStr">
+        <is>
+          <t>Oppenheimer-SpaceX.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B303" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="C303" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D303" s="8" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E303" s="8" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="F303" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G303" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Oppenheimer 2026-06-11): Terafab chip-manufacturing JV (SpaceX/Tesla/Intel); long-term goal 1TW of compute hardware per year</t>
+        </is>
+      </c>
+      <c r="H303" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I303" s="8" t="inlineStr">
+        <is>
+          <t>Oppenheimer-SpaceX.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B304" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="C304" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D304" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E304" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F304" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G304" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Oppenheimer 2026-06-11): Terafab chip-manufacturing JV with Tesla and Intel; BofA separately cites INTC Terafab engagements</t>
+        </is>
+      </c>
+      <c r="H304" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I304" s="8" t="inlineStr">
+        <is>
+          <t>Oppenheimer-SpaceX.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="8" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D305" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E305" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F305" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Oppenheimer 2026-06-11): OW initiation, $190 PT; space-based datacenters targeting 240GW vs ~100GW current global cloud capacity; economics unproven (?)</t>
+        </is>
+      </c>
+      <c r="H305" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I305" s="8" t="inlineStr">
+        <is>
+          <t>Oppenheimer-SpaceX.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="8" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="B306" s="8" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+      <c r="C306" s="8" t="inlineStr">
+        <is>
+          <t>provides EDA tools to</t>
+        </is>
+      </c>
+      <c r="D306" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E306" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F306" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G306" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, BofA 2026-06-11): Cadence 14A-node IP sign-up builds INTC external-foundry IP ecosystem</t>
+        </is>
+      </c>
+      <c r="H306" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I306" s="8" t="inlineStr">
+        <is>
+          <t>Intel double upgrade.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C307" s="8" t="inlineStr">
+        <is>
+          <t>invests in</t>
+        </is>
+      </c>
+      <c r="D307" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E307" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F307" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G307" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, SemiAnalysis 2026-06-11): Nvidia strategic investment at $23.28/sh alongside US govt 9.9% stake and SoftBank (~$20bn raised total)</t>
+        </is>
+      </c>
+      <c r="H307" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I307" s="8" t="inlineStr">
+        <is>
+          <t>英特尔应筹集资金 --- Intel Should Raise Capital.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="8" t="inlineStr">
+        <is>
+          <t>INNOLIGHT</t>
+        </is>
+      </c>
+      <c r="B308" s="8" t="inlineStr">
+        <is>
+          <t>Zhongji Innolight</t>
+        </is>
+      </c>
+      <c r="C308" s="8" t="inlineStr">
+        <is>
+          <t>supplies optical transceivers to</t>
+        </is>
+      </c>
+      <c r="D308" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E308" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F308" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G308" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, BofA 2026-06-10): deep relationship with Google, &gt;40% global 1.6T share; (VIEW): key beneficiary of potential Google Coherent-Lite adoption 2027-28</t>
+        </is>
+      </c>
+      <c r="H308" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I308" s="8" t="inlineStr">
+        <is>
+          <t>旭创.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="8" t="inlineStr">
+        <is>
+          <t>INNOLIGHT</t>
+        </is>
+      </c>
+      <c r="B309" s="8" t="inlineStr">
+        <is>
+          <t>Zhongji Innolight</t>
+        </is>
+      </c>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D309" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E309" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F309" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G309" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, BofA 2026-06-10): 1.6T demand strong into 2028 — supply/demand gap &gt;30%, extended lead times; NPO ~14% of 2027E revenue</t>
+        </is>
+      </c>
+      <c r="H309" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I309" s="8" t="inlineStr">
+        <is>
+          <t>旭创.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="8" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="B310" s="8" t="inlineStr">
+        <is>
+          <t>Tower Semiconductor</t>
+        </is>
+      </c>
+      <c r="C310" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D310" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E310" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F310" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G310" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, BofA 2026-06-10): US$1.3bn silicon-photonics contracts for 2027 with larger 2028 commitments — extended backlog, tight supply</t>
+        </is>
+      </c>
+      <c r="H310" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I310" s="8" t="inlineStr">
+        <is>
+          <t>旭创.pdf</t>
         </is>
       </c>
     </row>
@@ -18911,7 +20599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18963,24 +20651,24 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
         <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T_NET</t>
+          <t>T_INFER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optical &amp; Networking Buildout</t>
+          <t>AI Inference Demand</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18992,21 +20680,21 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T_CPO</t>
+          <t>T_NET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Co-Packaged Optics (CPO)</t>
+          <t>Optical &amp; Networking Buildout</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -19018,21 +20706,21 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T_INFER</t>
+          <t>T_CPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI Inference Demand</t>
+          <t>Co-Packaged Optics (CPO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -19044,10 +20732,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -19079,12 +20767,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T_TRAIN</t>
+          <t>T_POWER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AI Training Capex</t>
+          <t>Datacenter Power Demand</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -19096,21 +20784,21 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T_POWER</t>
+          <t>T_TRAIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Datacenter Power Demand</t>
+          <t>AI Training Capex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -19122,33 +20810,33 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
@@ -19157,53 +20845,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -19226,62 +20914,62 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -19313,24 +21001,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T_HBM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HBM Demand</t>
+          <t>Arm Holdings</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
         <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>9</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
@@ -19339,27 +21027,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>T_HBM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arm Holdings</t>
+          <t>HBM Demand</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -19391,50 +21079,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>7</v>
@@ -19443,38 +21131,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>SpaceX (Colossus compute)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -19483,36 +21171,36 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
@@ -19521,24 +21209,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -19547,24 +21235,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
@@ -19573,24 +21261,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T_GLASS</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Glass Core Substrate</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
         <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
@@ -19599,24 +21287,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>T_GLASS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Glass Core Substrate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>6</v>
@@ -19625,50 +21313,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -19677,24 +21365,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -19703,17 +21391,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -19729,17 +21417,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -19755,24 +21443,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -19781,24 +21469,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -19807,24 +21495,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -19833,24 +21521,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -19859,24 +21547,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -19885,24 +21573,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ZDT</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zhen Ding Technology</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -19911,102 +21599,102 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ZDT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Zhen Ding Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>4</v>
@@ -20015,17 +21703,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -20041,24 +21729,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -20067,24 +21755,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -20093,24 +21781,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -20119,17 +21807,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -20145,24 +21833,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -20171,17 +21859,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -20197,24 +21885,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>4</v>
@@ -20223,76 +21911,76 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -20301,17 +21989,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -20327,17 +22015,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -20353,24 +22041,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -20379,12 +22067,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -20393,10 +22081,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -20405,24 +22093,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -20431,24 +22119,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -20457,24 +22145,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -20483,24 +22171,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
         <v>1</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -20509,17 +22197,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -20535,24 +22223,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -20561,24 +22249,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -20587,24 +22275,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -20613,24 +22301,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -20639,12 +22327,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -20653,10 +22341,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -20665,24 +22353,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -20691,17 +22379,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SpaceX (Colossus compute)</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -20717,24 +22405,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -20743,24 +22431,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAMBRICON</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cambricon</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>3</v>
@@ -20769,64 +22457,64 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>CAMBRICON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>Cambricon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D73" t="n">
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -20847,17 +22535,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -20873,17 +22561,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -20899,17 +22587,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -20925,17 +22613,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -20951,17 +22639,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -20977,17 +22665,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -21003,17 +22691,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -21029,17 +22717,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -21055,12 +22743,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -21081,17 +22769,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -21107,17 +22795,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -21133,17 +22821,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -21159,24 +22847,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -21185,24 +22873,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
@@ -21289,76 +22977,76 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>SINOCERA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Sinocera</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
         <v>0</v>
       </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>INNOLIGHT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Zhongji Innolight</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="n">
         <v>0</v>
       </c>
-      <c r="E93" t="n">
-        <v>1</v>
-      </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
         <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -21367,24 +23055,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
         <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -21393,17 +23081,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -21419,17 +23107,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -21445,17 +23133,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -21471,12 +23159,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -21497,17 +23185,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>XLIGHT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cipher Mining</t>
+          <t>XLight</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -21523,17 +23211,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -21549,17 +23237,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SAMBANOVA</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Cipher Mining</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -21575,24 +23263,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BYTEDANCE</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
         <v>0</v>
-      </c>
-      <c r="E103" t="n">
-        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -21601,17 +23289,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LARGAN</t>
+          <t>SAMBANOVA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Largan Precision</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -21627,24 +23315,24 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>WIWYNN</t>
+          <t>BYTEDANCE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wiwynn</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
         <v>1</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -21653,17 +23341,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>LARGAN</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Camtek</t>
+          <t>Largan Precision</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -21679,24 +23367,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>WIWYNN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Naver</t>
+          <t>Wiwynn</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
         <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>1</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -21705,24 +23393,24 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DOOSAN</t>
+          <t>CAMT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Doosan</t>
+          <t>Camtek</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
         <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
@@ -21731,24 +23419,24 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HITACHI</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Naver</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
         <v>1</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
@@ -21757,24 +23445,24 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KIOXIA</t>
+          <t>DOOSAN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kioxia Holdings</t>
+          <t>Doosan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
         <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -21783,24 +23471,24 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ALLSPACE</t>
+          <t>HITACHI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ALL.SPACE</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
         <v>0</v>
-      </c>
-      <c r="E111" t="n">
-        <v>1</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -21809,17 +23497,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HANMI</t>
+          <t>KIOXIA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Hanmi Semiconductor</t>
+          <t>Kioxia Holdings</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -21835,24 +23523,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>ALLSPACE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>ALL.SPACE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
         <v>1</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -21861,12 +23549,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>HANMI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FormFactor</t>
+          <t>Hanmi Semiconductor</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -21887,12 +23575,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -21913,17 +23601,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IFX</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>FormFactor</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -21939,17 +23627,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -21959,6 +23647,318 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>IFX</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ENR</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Power Generation / Utilities</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DELTA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Delta Electronics</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ASE</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ASE Technology</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Seagate Technology</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WOLF</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Wolfspeed</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Navitas Semiconductor</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tower Semiconductor</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Foundry / Manufacturing</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -79,6 +79,10 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -143,7 +147,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -196,6 +200,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -7008,6 +7013,948 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>QUANTA</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Quanta Computer</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>2382.TW</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>ODM assembly</t>
+        </is>
+      </c>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>AI server racks, NVL72 systems</t>
+        </is>
+      </c>
+      <c r="J130" s="8" t="inlineStr">
+        <is>
+          <t>ODM assembler of Nvidia rack-scale AI systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>WISTRON</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>Wistron</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>3231.TW</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>ODM assembly</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I131" s="8" t="inlineStr">
+        <is>
+          <t>AI server racks, NVL72 systems</t>
+        </is>
+      </c>
+      <c r="J131" s="8" t="inlineStr">
+        <is>
+          <t>ODM assembler of Nvidia rack-scale AI systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>T_MLCC</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>AI Server MLCC Demand</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="n"/>
+      <c r="E132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>Demand Driver / Theme</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>Passive Components</t>
+        </is>
+      </c>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>High-capacitance MLCC for AI/GP servers</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>Demand driver: AI-server-grade MLCC shortage through 2028 lifting ASPs; passive-component bottleneck</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>SEMCO</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>009150.KS</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>ABF Substrate &amp; MLCC</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>AI-server MLCC, ABF/FCBGA substrates, silicon capacitors</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>Korea's leading passive-component &amp; package-substrate maker; AI-server MLCC + ABF substrate for accelerators/networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>Networking Systems</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Datacenter Networking</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>Optical transport, IP routing, datacenter networking</t>
+        </is>
+      </c>
+      <c r="J134" s="8" t="inlineStr">
+        <is>
+          <t>Telecom/datacenter networking &amp; optical vendor with growing AI back-end exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>NRG Energy</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>Power Generation / Utilities</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>Merchant Power / IPP</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>Texas/ERCOT generation, backup gas, datacenter PPAs</t>
+        </is>
+      </c>
+      <c r="J135" s="8" t="inlineStr">
+        <is>
+          <t>US merchant power generator positioned for Texas datacenter load growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>SHENGYI</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>Shengyi Technology</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>600183.SS</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>CCL / PCB materials</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I136" s="18" t="inlineStr">
+        <is>
+          <t>Copper-clad laminate (CCL), prepreg, PCB</t>
+        </is>
+      </c>
+      <c r="J136" s="18" t="inlineStr">
+        <is>
+          <t>High-end CCL supplier gaining AI share (NVIDIA/ASIC PCBs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>EMC</t>
+        </is>
+      </c>
+      <c r="B137" s="18" t="inlineStr">
+        <is>
+          <t>Elite Material</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D137" s="18" t="inlineStr">
+        <is>
+          <t>2383.TW</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>High-end CCL</t>
+        </is>
+      </c>
+      <c r="H137" s="18" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I137" s="18" t="inlineStr">
+        <is>
+          <t>High-speed/low-loss CCL (M8/M9)</t>
+        </is>
+      </c>
+      <c r="J137" s="18" t="inlineStr">
+        <is>
+          <t>Leading high-end CCL maker for AI HPC PCBs (NVIDIA/Google/AWS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>2327.TW</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>MLCC / passive components</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I138" s="18" t="inlineStr">
+        <is>
+          <t>MLCC, tantalum, resistors</t>
+        </is>
+      </c>
+      <c r="J138" s="18" t="inlineStr">
+        <is>
+          <t>Key AI-server passive-component beneficiary; pricing power</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>UNIMICRON</t>
+        </is>
+      </c>
+      <c r="B139" s="18" t="inlineStr">
+        <is>
+          <t>Unimicron</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D139" s="18" t="inlineStr">
+        <is>
+          <t>3037.TW</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
+          <t>ABF substrate</t>
+        </is>
+      </c>
+      <c r="H139" s="18" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I139" s="18" t="inlineStr">
+        <is>
+          <t>ABF/IC substrate, HDI PCB</t>
+        </is>
+      </c>
+      <c r="J139" s="18" t="inlineStr">
+        <is>
+          <t>#1 ABF substrate maker; AI substrate supply tightness</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>CHROMA</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t>Chroma ATE</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D140" s="18" t="inlineStr">
+        <is>
+          <t>2360.TW</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>Test (SLT/CPO/power)</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I140" s="18" t="inlineStr">
+        <is>
+          <t>SLT, optical-comm &amp; datacenter power test</t>
+        </is>
+      </c>
+      <c r="J140" s="18" t="inlineStr">
+        <is>
+          <t>~100% share in NVIDIA GPU SLT; CPO &amp; power testing leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>ADVANTEST</t>
+        </is>
+      </c>
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t>Advantest</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D141" s="18" t="inlineStr">
+        <is>
+          <t>6857.T</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G141" s="18" t="inlineStr">
+        <is>
+          <t>ATE / semiconductor test</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I141" s="18" t="inlineStr">
+        <is>
+          <t>SoC &amp; memory ATE testers</t>
+        </is>
+      </c>
+      <c r="J141" s="18" t="inlineStr">
+        <is>
+          <t>Leading ATE; memory-tester demand tied to HBM/DRAM capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t>BE Semiconductor (Besi)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D142" s="18" t="inlineStr">
+        <is>
+          <t>BESI.AS</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G142" s="18" t="inlineStr">
+        <is>
+          <t>Advanced-packaging equipment</t>
+        </is>
+      </c>
+      <c r="H142" s="18" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="I142" s="18" t="inlineStr">
+        <is>
+          <t>Die bonding, hybrid bonding, TCB, flip-chip</t>
+        </is>
+      </c>
+      <c r="J142" s="18" t="inlineStr">
+        <is>
+          <t>Advanced-packaging tool leader (hybrid bonding for HBM/CoWoS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>onsemi</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D143" s="18" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>Power semiconductors (SiC)</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I143" s="18" t="inlineStr">
+        <is>
+          <t>SiC/Si power devices, high-voltage</t>
+        </is>
+      </c>
+      <c r="J143" s="18" t="inlineStr">
+        <is>
+          <t>SiC power devices for datacenter AI power; analog recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>TeraWulf</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>Datacenter Infrastructure (REITs)</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>HPC colocation / neocloud (AI + BTC)</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I144" s="18" t="inlineStr">
+        <is>
+          <t>Power-rich AI/HPC hosting sites</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="inlineStr">
+        <is>
+          <t>AI digital-infrastructure host with power-rich sites for hyperscalers</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>T_PCB</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>AI PCB &amp; CCL Demand</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="D145" s="18" t="n"/>
+      <c r="E145" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>Demand Driver / Theme</t>
+        </is>
+      </c>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t>Demand driver</t>
+        </is>
+      </c>
+      <c r="H145" s="18" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="I145" s="18" t="inlineStr">
+        <is>
+          <t>AI server/switch PCB, CCL, substrate</t>
+        </is>
+      </c>
+      <c r="J145" s="18" t="inlineStr">
+        <is>
+          <t>Rising PCB layer count &amp; high-end CCL/substrate demand from AI hardware</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>MURATA</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>Murata Manufacturing</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D146" s="18" t="inlineStr">
+        <is>
+          <t>6981.T</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>MLCC / passive components</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I146" s="18" t="inlineStr">
+        <is>
+          <t>MLCC, inductors, RF modules</t>
+        </is>
+      </c>
+      <c r="J146" s="18" t="inlineStr">
+        <is>
+          <t>World No.1 MLCC maker (~41% share); key high-capacity AI-server/DC MLCC supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>TAIYOYUDEN</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>Taiyo Yuden</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>MLCC / passive components</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>MLCC, inductors</t>
+        </is>
+      </c>
+      <c r="J147" s="18" t="inlineStr">
+        <is>
+          <t>No.3 global MLCC maker (~11% share); AI-server/DC MLCC supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>IBIDEN</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="inlineStr">
+        <is>
+          <t>Ibiden</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>4062.T</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>ABF / package substrate</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I148" s="18" t="inlineStr">
+        <is>
+          <t>ABF/FCBGA package substrates</t>
+        </is>
+      </c>
+      <c r="J148" s="18" t="inlineStr">
+        <is>
+          <t>Leading ABF package-substrate maker for NVIDIA accelerators and Intel server CPUs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -7022,7 +7969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I310"/>
+  <dimension ref="A1:I349"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -7999,16 +8946,16 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Marvell among TSMC's top 5nm customers; multiple designs under contract (FACT, EE Times Asia)</t>
+          <t>Marvell among TSMC's top 5nm customers; multiple designs under contract (FACT, EE Times Asia) ; (FACT, X-scan 2026-06-12): Marvell Teralynx T100 102.4Tbps switch built on TSMC 3nm, launched early Jun 2026</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
@@ -8298,12 +9245,12 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>(FACT, X-scan 2026-06-05): Jensen certified SK Hynix for Vera Rubin HBM4 supply (est 60-70% of volume); press-corroborated; lead HBM supplier</t>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified SK Hynix for Vera Rubin HBM4 supply (est 60-70% of volume); press-corroborated; lead HBM supplier ; HBM4 full-production cert, ~60-70% allocation (FACT, X-scan 2026-06-12)</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
@@ -9740,12 +10687,12 @@
       </c>
       <c r="G64" s="15" t="inlineStr">
         <is>
-          <t>GB200 racks</t>
+          <t>GB200 racks ; also named assembler of NVIDIA Vera Rubin NVL72 rack-scale systems (FACT, X-scan 2026-06-12)</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I64" s="15" t="n"/>
@@ -10820,7 +11767,7 @@
       </c>
       <c r="G92" s="15" t="inlineStr">
         <is>
-          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply</t>
+          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply | (VIEW, UBS 2026-06-09): memory revs +318% YoY '26; DRAM tight/undersupplied under LTA</t>
         </is>
       </c>
       <c r="H92" s="15" t="inlineStr">
@@ -10861,7 +11808,7 @@
       </c>
       <c r="G93" s="15" t="inlineStr">
         <is>
-          <t>None | (FACT, X-scan 2026-06-11): entire 2026 HBM capacity booked/sold out under binding contracts; HBM4 stack shown at COMPUTEX 2026</t>
+          <t>None | (FACT, X-scan 2026-06-11): entire 2026 HBM capacity booked/sold out under binding contracts; HBM4 stack shown at COMPUTEX 2026 | (VIEW, UBS 2026-06-09): structural memory shortage; DRAM/NAND tight under LTA; PT $1,625</t>
         </is>
       </c>
       <c r="H93" s="15" t="inlineStr">
@@ -10902,7 +11849,7 @@
       </c>
       <c r="G94" s="15" t="inlineStr">
         <is>
-          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply</t>
+          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply | (VIEW, UBS 2026-06-09): memory undersupplied through '27; DRAM-led WFE buildout</t>
         </is>
       </c>
       <c r="H94" s="15" t="inlineStr">
@@ -13208,7 +14155,7 @@
       </c>
       <c r="G148" s="16" t="inlineStr">
         <is>
-          <t>(VIEW, Goldman Sachs 2026-05-28): AI-driven step-up in EUV demand; &gt;60 EUV systems 2026, path to &gt;80 in 2027; Buy, PT EUR1,600</t>
+          <t>(VIEW, Goldman Sachs 2026-05-28): AI-driven step-up in EUV demand; &gt;60 EUV systems 2026, path to &gt;80 in 2027; Buy, PT EUR1,600 | (VIEW, UBS 2026-06-09): litho not a WFE constraint; capacity for &gt;100 EUV shipments/yr '27-'28, &gt;$46B systems rev '27</t>
         </is>
       </c>
       <c r="H148" s="16" t="inlineStr">
@@ -16348,7 +17295,7 @@
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
-          <t>(VIEW, Funda-AI 2026-06-03): Marvell to design the networking chip in the Google/Intel IPU program (?)</t>
+          <t>(VIEW, Funda-AI 2026-06-03): Marvell to design the networking chip in the Google/Intel IPU program (?) | (FACT, X-scan 2026-06-16): Marvell custom-ASIC/XPU program with Alphabet among named hyperscaler customers — corroborates Marvell–Alphabet custom-silicon relationship</t>
         </is>
       </c>
       <c r="H222" s="8" t="inlineStr">
@@ -16393,7 +17340,7 @@
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
-          <t>(FACT, Goldman 2026-05-28): Bloom Energy partnership accelerates Nebius power permitting/deployment (800MW-1GW connected 2026)</t>
+          <t>(FACT, Goldman 2026-05-28): Bloom Energy partnership accelerates Nebius power permitting/deployment (800MW-1GW connected 2026) | (FACT, X-scan 2026-06-16): Bloom–Nebius master agreement ~$2.6B / 328 MW installed fuel-cell capacity</t>
         </is>
       </c>
       <c r="H223" s="8" t="inlineStr">
@@ -16708,12 +17655,12 @@
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>(FACT, X-scan 2026-06-05): Jensen certified Micron for Vera Rubin HBM4 supply; press-corroborated</t>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified Micron for Vera Rubin HBM4 supply; press-corroborated ; HBM4 full-production cert, remainder of allocation (FACT, X-scan 2026-06-12)</t>
         </is>
       </c>
       <c r="H230" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I230" s="8" t="inlineStr">
@@ -16753,12 +17700,12 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>(FACT, X-scan 2026-06-05): Jensen certified Samsung for Vera Rubin HBM4 supply; press-corroborated</t>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified Samsung for Vera Rubin HBM4 supply; press-corroborated ; HBM4 full-production cert, ~25-30% allocation (FACT, X-scan 2026-06-12)</t>
         </is>
       </c>
       <c r="H231" s="8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I231" s="8" t="inlineStr">
@@ -18013,7 +18960,7 @@
       </c>
       <c r="G259" s="8" t="inlineStr">
         <is>
-          <t>(FACT, X-scan 2026-06-08): NVIDIA–SK Hynix multiyear partnership co-developing SOCAMM2/HBM4 for Vera Rubin; applies CUDA-X, PhysicsNeMo, Omniverse to SK Hynix chip design, TCAD and autonomous fab digital twins</t>
+          <t>(FACT, X-scan 2026-06-08): NVIDIA–SK Hynix multiyear partnership co-developing SOCAMM2/HBM4 for Vera Rubin; applies CUDA-X, PhysicsNeMo, Omniverse to SK Hynix chip design, TCAD and autonomous fab digital twins | (FACT, X-scan 2026-06-13): partnership extended to AI-driven fab design (Omniverse digital twins) + next-gen memory for AI factories (NVIDIA newsroom 2026-06-11)</t>
         </is>
       </c>
       <c r="H259" s="8" t="inlineStr">
@@ -19003,7 +19950,7 @@
       </c>
       <c r="G281" s="8" t="inlineStr">
         <is>
-          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; industry fundamentals already at levels previously expected for 2028</t>
+          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; industry fundamentals already at levels previously expected for 2028 | (VIEW, UBS 2026-06-09): WFE supercycle, ~$198B '27 / ~$247.5B '28; AMAT Most Preferred, PT $570</t>
         </is>
       </c>
       <c r="H281" s="8" t="inlineStr">
@@ -19048,7 +19995,7 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; fundamentals at levels previously expected for 2028</t>
+          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; fundamentals at levels previously expected for 2028 | (VIEW, UBS 2026-06-09): WFE supercycle beneficiary; LRCX preferred, PT $375</t>
         </is>
       </c>
       <c r="H282" s="8" t="inlineStr">
@@ -19093,7 +20040,7 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; fundamentals at levels previously expected for 2028</t>
+          <t>(VIEW, Barclays 2026-06-10): preferred beneficiary of semicap capex cycle; fundamentals at levels previously expected for 2028 | (VIEW, UBS 2026-06-09): WFE supercycle but KLAC ~26x '28E PE leaves less upside; PT $2,180</t>
         </is>
       </c>
       <c r="H283" s="8" t="inlineStr">
@@ -19588,7 +20535,7 @@
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>(FACT, Jefferies 2026-06-08): expanded Oracle–Bloom Energy partnership adds faster on-site fuel-cell power that bypasses grid constraints for OCI AI buildout</t>
+          <t>(FACT, Jefferies 2026-06-08): expanded Oracle–Bloom Energy partnership adds faster on-site fuel-cell power that bypasses grid constraints for OCI AI buildout | (FACT, X-scan 2026-06-16): up to 2.8 GW of fuel-cell power agreed for Oracle AI data centers</t>
         </is>
       </c>
       <c r="H294" s="8" t="inlineStr">
@@ -19633,7 +20580,7 @@
       </c>
       <c r="G295" s="8" t="inlineStr">
         <is>
-          <t>(VIEW, JPM 2026-06-11): HDD pricing accelerating faster than expected on AI demand; LTAs support durable pricing and margin expansion</t>
+          <t>(VIEW, JPM 2026-06-11): HDD pricing accelerating faster than expected on AI demand; LTAs support durable pricing and margin expansion ; corroborated by MS PT raises (WDC-&gt;$650, STX-&gt;$1,035), Narrative Atlas 2026-06-15</t>
         </is>
       </c>
       <c r="H295" s="8" t="inlineStr">
@@ -19678,7 +20625,7 @@
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>(VIEW, JPM 2026-06-11): HDD pricing accelerating faster than expected on AI demand; LTAs support durable pricing and margin expansion</t>
+          <t>(VIEW, JPM 2026-06-11): HDD pricing accelerating faster than expected on AI demand; LTAs support durable pricing and margin expansion ; corroborated by MS PT raises (WDC-&gt;$650, STX-&gt;$1,035), Narrative Atlas 2026-06-15</t>
         </is>
       </c>
       <c r="H296" s="8" t="inlineStr">
@@ -20319,6 +21266,1761 @@
       <c r="I310" s="8" t="inlineStr">
         <is>
           <t>旭创.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="8" t="inlineStr">
+        <is>
+          <t>QUANTA</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="inlineStr">
+        <is>
+          <t>Quanta Computer</t>
+        </is>
+      </c>
+      <c r="C311" s="8" t="inlineStr">
+        <is>
+          <t>assembles AI systems for</t>
+        </is>
+      </c>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F311" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G311" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-12): named assembler of NVIDIA Vera Rubin NVL72 rack-scale systems</t>
+        </is>
+      </c>
+      <c r="H311" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I311" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-12-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="8" t="inlineStr">
+        <is>
+          <t>WISTRON</t>
+        </is>
+      </c>
+      <c r="B312" s="8" t="inlineStr">
+        <is>
+          <t>Wistron</t>
+        </is>
+      </c>
+      <c r="C312" s="8" t="inlineStr">
+        <is>
+          <t>assembles AI systems for</t>
+        </is>
+      </c>
+      <c r="D312" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E312" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F312" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G312" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-12): named assembler of NVIDIA Vera Rubin NVL72 rack-scale systems</t>
+        </is>
+      </c>
+      <c r="H312" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I312" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-12-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="8" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B313" s="8" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C313" s="8" t="inlineStr">
+        <is>
+          <t>manufactures chips for</t>
+        </is>
+      </c>
+      <c r="D313" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E313" s="8" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F313" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G313" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-13): Alphabet ordered &gt;3,000,000 custom TPUs from Intel to be built in 2028 — first time Intel acts as Google's AI-chip contract manufacturer (The Information ~2026-06-08)</t>
+        </is>
+      </c>
+      <c r="H313" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="I313" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-13-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="8" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B314" s="8" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="C314" s="8" t="inlineStr">
+        <is>
+          <t>partners with</t>
+        </is>
+      </c>
+      <c r="D314" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E314" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F314" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G314" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-13): TSMC adopting NVIDIA accelerated computing/CUDA-X + AI across semiconductor design and fab manufacturing (NVIDIA newsroom 2026-06-11)</t>
+        </is>
+      </c>
+      <c r="H314" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="I314" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-13-2005-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="8" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="B315" s="8" t="inlineStr">
+        <is>
+          <t>Teradyne</t>
+        </is>
+      </c>
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D315" s="8" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E315" s="8" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F315" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G315" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, J.P. Morgan 2026-06-12 via Narrative Atlas): robust memory test demand; multi-year memory-capex tailwind; 2nd hyperscaler ATE qualification</t>
+        </is>
+      </c>
+      <c r="H315" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I315" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="8" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B316" s="8" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C316" s="8" t="inlineStr">
+        <is>
+          <t>supplies AI accelerators to</t>
+        </is>
+      </c>
+      <c r="D316" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="E316" s="8" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F316" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G316" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Wells Fargo 2026-06-12 via Narrative Atlas): AWS identified as likely lead hyperscale customer for Qualcomm datacenter AI accelerators; per-GW revenue opportunity (?)</t>
+        </is>
+      </c>
+      <c r="H316" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I316" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="8" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D317" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F317" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G317" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, J.P. Morgan 2026-06-12 via Narrative Atlas): strong AI/cloud orders + new optical products; market underestimating optical &amp; datacenter-networking operating leverage; PT raised</t>
+        </is>
+      </c>
+      <c r="H317" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I317" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="8" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B318" s="8" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="C318" s="8" t="inlineStr">
+        <is>
+          <t>supplies switches to</t>
+        </is>
+      </c>
+      <c r="D318" s="8" t="inlineStr">
+        <is>
+          <t>ANTHROPIC</t>
+        </is>
+      </c>
+      <c r="E318" s="8" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="F318" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G318" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Evercore ISI 2026-06-12 via Narrative Atlas): underappreciated multi-billion-dollar revenue opportunity with Anthropic; diversifies customer base (?)</t>
+        </is>
+      </c>
+      <c r="H318" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I318" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="8" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr">
+        <is>
+          <t>NRG Energy</t>
+        </is>
+      </c>
+      <c r="C319" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D319" s="8" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F319" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G319" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06-11): Texas/ERCOT datacenter load growth; new-build incentives + backup-generation underwriting under WLPUN/PCLR</t>
+        </is>
+      </c>
+      <c r="H319" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I319" s="8" t="inlineStr">
+        <is>
+          <t>CITI-US Diversified Utilities：Texas Power Field Trip Takes – Let's Get Real Abou.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="8" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B320" s="8" t="inlineStr">
+        <is>
+          <t>KLA Corporation</t>
+        </is>
+      </c>
+      <c r="C320" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D320" s="8" t="inlineStr">
+        <is>
+          <t>T_COWOS</t>
+        </is>
+      </c>
+      <c r="E320" s="8" t="inlineStr">
+        <is>
+          <t>CoWoS Advanced Packaging</t>
+        </is>
+      </c>
+      <c r="F320" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G320" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, J.P. Morgan 2026-06-12): ~58% process-control share (~7.6x nearest rival); gatekeeper of leading-edge &amp; advanced-packaging yield; advanced-packaging wafer-level inspection share gains; premium pricing</t>
+        </is>
+      </c>
+      <c r="H320" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I320" s="8" t="inlineStr">
+        <is>
+          <t>J.P. Morgan-KLA Corporation（KLAC.US）KLAC Extends Process Control #1 Market Share Leadership in 2025； Confident on Maintaining Premium Margin Profi.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="8" t="inlineStr">
+        <is>
+          <t>SEMCO</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="C321" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D321" s="8" t="inlineStr">
+        <is>
+          <t>T_MLCC</t>
+        </is>
+      </c>
+      <c r="E321" s="8" t="inlineStr">
+        <is>
+          <t>AI Server MLCC Demand</t>
+        </is>
+      </c>
+      <c r="F321" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G321" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, J.P. Morgan 2026-06-12): AI-server-grade MLCC design wins; capacity booked/tight; multi-year shortage from 2027; high-50% ASP growth</t>
+        </is>
+      </c>
+      <c r="H321" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I321" s="8" t="inlineStr">
+        <is>
+          <t>J.P. Morgan-Samsung Electro~Mechanics（009150.KS）Leveraging up~cycle with full~sc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="8" t="inlineStr">
+        <is>
+          <t>SEMCO</t>
+        </is>
+      </c>
+      <c r="B322" s="8" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="C322" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D322" s="8" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E322" s="8" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F322" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G322" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, J.P. Morgan 2026-06-12): ABF substrate mix shifting to AI accelerator/networking; 2026-27 ABF capacity almost fully booked; renewed pricing quotes</t>
+        </is>
+      </c>
+      <c r="H322" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I322" s="8" t="inlineStr">
+        <is>
+          <t>J.P. Morgan-Samsung Electro~Mechanics（009150.KS）Leveraging up~cycle with full~sc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="8" t="inlineStr">
+        <is>
+          <t>SINOCERA</t>
+        </is>
+      </c>
+      <c r="B323" s="8" t="inlineStr">
+        <is>
+          <t>Sinocera</t>
+        </is>
+      </c>
+      <c r="C323" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D323" s="8" t="inlineStr">
+        <is>
+          <t>T_MLCC</t>
+        </is>
+      </c>
+      <c r="E323" s="8" t="inlineStr">
+        <is>
+          <t>AI Server MLCC Demand</t>
+        </is>
+      </c>
+      <c r="F323" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G323" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, J.P. Morgan 2026-06-12): upstream MLCC dielectric powder into AI-server MLCC shortage; demand &amp; ASP rising</t>
+        </is>
+      </c>
+      <c r="H323" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I323" s="8" t="inlineStr">
+        <is>
+          <t>JPM_Asian_MLCC_Industry__2026-06-12_5333437.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B324" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C324" s="18" t="inlineStr">
+        <is>
+          <t>drives demand for</t>
+        </is>
+      </c>
+      <c r="D324" s="18" t="inlineStr">
+        <is>
+          <t>T_PCB</t>
+        </is>
+      </c>
+      <c r="E324" s="18" t="inlineStr">
+        <is>
+          <t>AI PCB &amp; CCL Demand</t>
+        </is>
+      </c>
+      <c r="F324" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G324" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW/EST, JPM/Jefferies 2026-06): Nvidia AI CCL demand ~1.5m sheets/mo by 2027; PCB layer count &amp; CCL content per chip rising</t>
+        </is>
+      </c>
+      <c r="H324" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I324" s="18" t="inlineStr">
+        <is>
+          <t>JPM_Asia_Passive_Compone_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="18" t="inlineStr">
+        <is>
+          <t>SHENGYI</t>
+        </is>
+      </c>
+      <c r="B325" s="18" t="inlineStr">
+        <is>
+          <t>Shengyi Technology</t>
+        </is>
+      </c>
+      <c r="C325" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D325" s="18" t="inlineStr">
+        <is>
+          <t>T_PCB</t>
+        </is>
+      </c>
+      <c r="E325" s="18" t="inlineStr">
+        <is>
+          <t>AI PCB &amp; CCL Demand</t>
+        </is>
+      </c>
+      <c r="F325" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G325" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Jefferies 2026-06-13): high-end AI CCL share gains; CCL shortage/tight supply driving ASP up</t>
+        </is>
+      </c>
+      <c r="H325" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I325" s="18" t="inlineStr">
+        <is>
+          <t>Jefferies-shengyi.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="18" t="inlineStr">
+        <is>
+          <t>SHENGYI</t>
+        </is>
+      </c>
+      <c r="B326" s="18" t="inlineStr">
+        <is>
+          <t>Shengyi Technology</t>
+        </is>
+      </c>
+      <c r="C326" s="18" t="inlineStr">
+        <is>
+          <t>supplies CCL to</t>
+        </is>
+      </c>
+      <c r="D326" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E326" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F326" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G326" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Jefferies 2026-06-13): high-end CCL share gain at NVIDIA; ASIC penetration (?)</t>
+        </is>
+      </c>
+      <c r="H326" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I326" s="18" t="inlineStr">
+        <is>
+          <t>Jefferies-shengyi.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="18" t="inlineStr">
+        <is>
+          <t>EMC</t>
+        </is>
+      </c>
+      <c r="B327" s="18" t="inlineStr">
+        <is>
+          <t>Elite Material</t>
+        </is>
+      </c>
+      <c r="C327" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D327" s="18" t="inlineStr">
+        <is>
+          <t>T_PCB</t>
+        </is>
+      </c>
+      <c r="E327" s="18" t="inlineStr">
+        <is>
+          <t>AI PCB &amp; CCL Demand</t>
+        </is>
+      </c>
+      <c r="F327" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G327" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): major beneficiary of high-end CCL upgrade; m/s in key HPC projects (NVIDIA/Google/AWS)</t>
+        </is>
+      </c>
+      <c r="H327" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I327" s="18" t="inlineStr">
+        <is>
+          <t>JPM_Asia_Passive_Compone_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="18" t="inlineStr">
+        <is>
+          <t>UNIMICRON</t>
+        </is>
+      </c>
+      <c r="B328" s="18" t="inlineStr">
+        <is>
+          <t>Unimicron</t>
+        </is>
+      </c>
+      <c r="C328" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D328" s="18" t="inlineStr">
+        <is>
+          <t>T_COWOS</t>
+        </is>
+      </c>
+      <c r="E328" s="18" t="inlineStr">
+        <is>
+          <t>CoWoS Advanced Packaging</t>
+        </is>
+      </c>
+      <c r="F328" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G328" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): ABF substrate entering unprecedented supply tightness; AI chip size/layer migration</t>
+        </is>
+      </c>
+      <c r="H328" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I328" s="18" t="inlineStr">
+        <is>
+          <t>JPM_Asia_Passive_Compone_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="18" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="B329" s="18" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="C329" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D329" s="18" t="inlineStr">
+        <is>
+          <t>T_MLCC</t>
+        </is>
+      </c>
+      <c r="E329" s="18" t="inlineStr">
+        <is>
+          <t>AI Server MLCC Demand</t>
+        </is>
+      </c>
+      <c r="F329" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G329" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM/GFHK 2026-06-15): lead AI-server MLCC/passives beneficiary; low-cap pricing power, lead-time extension</t>
+        </is>
+      </c>
+      <c r="H329" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I329" s="18" t="inlineStr">
+        <is>
+          <t>JPM_Asia_Passive_Compone_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B330" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C330" s="18" t="inlineStr">
+        <is>
+          <t>drives demand for</t>
+        </is>
+      </c>
+      <c r="D330" s="18" t="inlineStr">
+        <is>
+          <t>T_MLCC</t>
+        </is>
+      </c>
+      <c r="E330" s="18" t="inlineStr">
+        <is>
+          <t>AI Server MLCC Demand</t>
+        </is>
+      </c>
+      <c r="F330" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G330" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, GFHK/JPM 2026-06-15): VR200 NVL72 ~550k MLCCs vs ~300k GB200; ultra-high-cap ~60% of AI demand</t>
+        </is>
+      </c>
+      <c r="H330" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I330" s="18" t="inlineStr">
+        <is>
+          <t>GFHK - MLCC.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="18" t="inlineStr">
+        <is>
+          <t>ADVANTEST</t>
+        </is>
+      </c>
+      <c r="B331" s="18" t="inlineStr">
+        <is>
+          <t>Advantest</t>
+        </is>
+      </c>
+      <c r="C331" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D331" s="18" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E331" s="18" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F331" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G331" s="18" t="inlineStr">
+        <is>
+          <t>(FACT, Bernstein 2026-06-15): Korea memory-tester import +103% YoY; HBM/DRAM capex driven</t>
+        </is>
+      </c>
+      <c r="H331" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I331" s="18" t="inlineStr">
+        <is>
+          <t>Bernstein South Korea Equipment Import Tracker-260615.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="18" t="inlineStr">
+        <is>
+          <t>ADVANTEST</t>
+        </is>
+      </c>
+      <c r="B332" s="18" t="inlineStr">
+        <is>
+          <t>Advantest</t>
+        </is>
+      </c>
+      <c r="C332" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D332" s="18" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E332" s="18" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F332" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G332" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06-15): AI SoC/GPU test demand; pricing power on tight supply</t>
+        </is>
+      </c>
+      <c r="H332" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I332" s="18" t="inlineStr">
+        <is>
+          <t>Bernstein South Korea Equipment Import Tracker-260615.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="18" t="inlineStr">
+        <is>
+          <t>CHROMA</t>
+        </is>
+      </c>
+      <c r="B333" s="18" t="inlineStr">
+        <is>
+          <t>Chroma ATE</t>
+        </is>
+      </c>
+      <c r="C333" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D333" s="18" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E333" s="18" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F333" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G333" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): ~100% share (sole) in NVIDIA GPU SLT equipment; testing time &amp; TDP rising</t>
+        </is>
+      </c>
+      <c r="H333" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I333" s="18" t="inlineStr">
+        <is>
+          <t>JPM_Asia_Passive_Compone_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="18" t="inlineStr">
+        <is>
+          <t>CHROMA</t>
+        </is>
+      </c>
+      <c r="B334" s="18" t="inlineStr">
+        <is>
+          <t>Chroma ATE</t>
+        </is>
+      </c>
+      <c r="C334" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D334" s="18" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E334" s="18" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F334" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G334" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): CPO testing + optical-comm testing at 100%+ CAGR</t>
+        </is>
+      </c>
+      <c r="H334" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I334" s="18" t="inlineStr">
+        <is>
+          <t>JPM_Asia_Passive_Compone_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="18" t="inlineStr">
+        <is>
+          <t>CHROMA</t>
+        </is>
+      </c>
+      <c r="B335" s="18" t="inlineStr">
+        <is>
+          <t>Chroma ATE</t>
+        </is>
+      </c>
+      <c r="C335" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D335" s="18" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E335" s="18" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F335" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G335" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): leader in AI datacenter power testing (PSU/HVDC), 100%+ CAGR</t>
+        </is>
+      </c>
+      <c r="H335" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I335" s="18" t="inlineStr">
+        <is>
+          <t>JPM_Asia_Passive_Compone_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="18" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B336" s="18" t="inlineStr">
+        <is>
+          <t>BE Semiconductor (Besi)</t>
+        </is>
+      </c>
+      <c r="C336" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D336" s="18" t="inlineStr">
+        <is>
+          <t>T_COWOS</t>
+        </is>
+      </c>
+      <c r="E336" s="18" t="inlineStr">
+        <is>
+          <t>CoWoS Advanced Packaging</t>
+        </is>
+      </c>
+      <c r="F336" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G336" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-15): hybrid bonding/TCB/flip-chip for advanced packaging; China HE packaging push</t>
+        </is>
+      </c>
+      <c r="H336" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I336" s="18" t="inlineStr">
+        <is>
+          <t>BE.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="18" t="inlineStr">
+        <is>
+          <t>BESI</t>
+        </is>
+      </c>
+      <c r="B337" s="18" t="inlineStr">
+        <is>
+          <t>BE Semiconductor (Besi)</t>
+        </is>
+      </c>
+      <c r="C337" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D337" s="18" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E337" s="18" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F337" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G337" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-15): hybrid bonding adoption for HBM stacking</t>
+        </is>
+      </c>
+      <c r="H337" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I337" s="18" t="inlineStr">
+        <is>
+          <t>BE.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B338" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C338" s="18" t="inlineStr">
+        <is>
+          <t>drives demand for</t>
+        </is>
+      </c>
+      <c r="D338" s="18" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E338" s="18" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F338" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G338" s="18" t="inlineStr">
+        <is>
+          <t>(FACT, Narrative Atlas 2026-06-15): Vera Rubin adopts 800V HVDC architecture, shipments commencing Q3</t>
+        </is>
+      </c>
+      <c r="H338" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I338" s="18" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="18" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B339" s="18" t="inlineStr">
+        <is>
+          <t>onsemi</t>
+        </is>
+      </c>
+      <c r="C339" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D339" s="18" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E339" s="18" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F339" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G339" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06-15): differentiated SiC portfolio; datacenter power demand &amp; firm pricing; PT raised</t>
+        </is>
+      </c>
+      <c r="H339" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I339" s="18" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="18" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="B340" s="18" t="inlineStr">
+        <is>
+          <t>TeraWulf</t>
+        </is>
+      </c>
+      <c r="C340" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D340" s="18" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E340" s="18" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F340" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G340" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, BofA 2026-06-15): AI digital-infra transformation; power-rich sites attract hyperscale tenants; initiated Buy PT $34</t>
+        </is>
+      </c>
+      <c r="H340" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I340" s="18" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="18" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B341" s="18" t="inlineStr">
+        <is>
+          <t>Astera Labs</t>
+        </is>
+      </c>
+      <c r="C341" s="18" t="inlineStr">
+        <is>
+          <t>supplies interconnect to</t>
+        </is>
+      </c>
+      <c r="D341" s="18" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E341" s="18" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="F341" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Northland 2026-06-15): scale-up switch (Scorpio) deployments growing with AMD (?)</t>
+        </is>
+      </c>
+      <c r="H341" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I341" s="18" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B342" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C342" s="18" t="inlineStr">
+        <is>
+          <t>invests in</t>
+        </is>
+      </c>
+      <c r="D342" s="18" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="E342" s="18" t="inlineStr">
+        <is>
+          <t>Lumentum</t>
+        </is>
+      </c>
+      <c r="F342" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G342" s="18" t="inlineStr">
+        <is>
+          <t>(FACT, Morgan Stanley 2026-06-12): equity investment + optical capacity commitment (limits supplier swap)</t>
+        </is>
+      </c>
+      <c r="H342" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I342" s="18" t="inlineStr">
+        <is>
+          <t>大摩 NPO CPO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B343" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C343" s="18" t="inlineStr">
+        <is>
+          <t>invests in</t>
+        </is>
+      </c>
+      <c r="D343" s="18" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="E343" s="18" t="inlineStr">
+        <is>
+          <t>Coherent</t>
+        </is>
+      </c>
+      <c r="F343" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G343" s="18" t="inlineStr">
+        <is>
+          <t>(FACT, Morgan Stanley 2026-06-12): equity investment + optical capacity commitment</t>
+        </is>
+      </c>
+      <c r="H343" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I343" s="18" t="inlineStr">
+        <is>
+          <t>大摩 NPO CPO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B344" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C344" s="18" t="inlineStr">
+        <is>
+          <t>invests in</t>
+        </is>
+      </c>
+      <c r="D344" s="18" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="E344" s="18" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="F344" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G344" s="18" t="inlineStr">
+        <is>
+          <t>(FACT, Morgan Stanley 2026-06-12): equity investment + optical capacity commitment</t>
+        </is>
+      </c>
+      <c r="H344" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I344" s="18" t="inlineStr">
+        <is>
+          <t>大摩 NPO CPO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="18" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B345" s="18" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="C345" s="18" t="inlineStr">
+        <is>
+          <t>manufactures chips for</t>
+        </is>
+      </c>
+      <c r="D345" s="18" t="inlineStr">
+        <is>
+          <t>SKHYNIX</t>
+        </is>
+      </c>
+      <c r="E345" s="18" t="inlineStr">
+        <is>
+          <t>SK Hynix</t>
+        </is>
+      </c>
+      <c r="F345" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G345" s="18" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-16): TSMC 3nm logic base die used in SK Hynix 12-layer HBM4E; HBM4 base-die partnership (Chey–C.C. Wei, 6/3)</t>
+        </is>
+      </c>
+      <c r="H345" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="I345" s="18" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-16-0404-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="18" t="inlineStr">
+        <is>
+          <t>MURATA</t>
+        </is>
+      </c>
+      <c r="B346" s="18" t="inlineStr">
+        <is>
+          <t>Murata Manufacturing</t>
+        </is>
+      </c>
+      <c r="C346" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D346" s="18" t="inlineStr">
+        <is>
+          <t>T_MLCC</t>
+        </is>
+      </c>
+      <c r="E346" s="18" t="inlineStr">
+        <is>
+          <t>AI Server MLCC Demand</t>
+        </is>
+      </c>
+      <c r="F346" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G346" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-16): No.1 global MLCC share (~40.8%); top pick on small high-capacity MLCCs for AI server/DC; AI/DC MLCC demand ~doubling annually</t>
+        </is>
+      </c>
+      <c r="H346" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I346" s="18" t="inlineStr">
+        <is>
+          <t>大摩-电子元器件MLCC.pdf; MS 上调村田 MLCC.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="18" t="inlineStr">
+        <is>
+          <t>TAIYOYUDEN</t>
+        </is>
+      </c>
+      <c r="B347" s="18" t="inlineStr">
+        <is>
+          <t>Taiyo Yuden</t>
+        </is>
+      </c>
+      <c r="C347" s="18" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D347" s="18" t="inlineStr">
+        <is>
+          <t>T_MLCC</t>
+        </is>
+      </c>
+      <c r="E347" s="18" t="inlineStr">
+        <is>
+          <t>AI Server MLCC Demand</t>
+        </is>
+      </c>
+      <c r="F347" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G347" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-16): No.3 global MLCC share (~11.3%); rising AI/DC MLCC sales but only modest mix benefit; MS downgraded to UW on valuation</t>
+        </is>
+      </c>
+      <c r="H347" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I347" s="18" t="inlineStr">
+        <is>
+          <t>大摩-电子元器件MLCC.pdf; MS 上调村田 MLCC.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="18" t="inlineStr">
+        <is>
+          <t>IBIDEN</t>
+        </is>
+      </c>
+      <c r="B348" s="18" t="inlineStr">
+        <is>
+          <t>Ibiden</t>
+        </is>
+      </c>
+      <c r="C348" s="18" t="inlineStr">
+        <is>
+          <t>supplies package substrate to</t>
+        </is>
+      </c>
+      <c r="D348" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E348" s="18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F348" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G348" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-16): OP growth driven by high share in NVIDIA-related ABF/package-substrate demand</t>
+        </is>
+      </c>
+      <c r="H348" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I348" s="18" t="inlineStr">
+        <is>
+          <t>大摩-电子元器件MLCC.pdf; MS 上调村田 MLCC.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="18" t="inlineStr">
+        <is>
+          <t>IBIDEN</t>
+        </is>
+      </c>
+      <c r="B349" s="18" t="inlineStr">
+        <is>
+          <t>Ibiden</t>
+        </is>
+      </c>
+      <c r="C349" s="18" t="inlineStr">
+        <is>
+          <t>supplies package substrate to</t>
+        </is>
+      </c>
+      <c r="D349" s="18" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E349" s="18" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F349" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G349" s="18" t="inlineStr">
+        <is>
+          <t>(VIEW, Morgan Stanley 2026-06-16): ABF package-substrate sales for Intel server CPUs (Diamond Rapids/Xeon)</t>
+        </is>
+      </c>
+      <c r="H349" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I349" s="18" t="inlineStr">
+        <is>
+          <t>大摩-电子元器件MLCC.pdf; MS 上调村田 MLCC.pdf</t>
         </is>
       </c>
     </row>
@@ -20599,7 +23301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20651,13 +23353,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -20706,10 +23408,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -20732,62 +23434,62 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>T_POWER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Datacenter Power Demand</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T_POWER</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Datacenter Power Demand</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -20810,59 +23512,59 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
         <v>11</v>
       </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>15</v>
@@ -20871,27 +23573,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -20914,10 +23616,10 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -20940,10 +23642,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -20966,21 +23668,21 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T_CHINA</t>
+          <t>T_HBM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>China Indigenous AI Buildout</t>
+          <t>HBM Demand</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -20992,59 +23694,59 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>T_CHINA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arm Holdings</t>
+          <t>China Indigenous AI Buildout</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T_HBM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HBM Demand</t>
+          <t>Arm Holdings</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
         <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
@@ -21209,24 +23911,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -21235,17 +23937,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -21261,24 +23963,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
@@ -21287,17 +23989,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T_GLASS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Glass Core Substrate</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -21313,24 +24015,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>6</v>
@@ -21339,206 +24041,206 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>T_GLASS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>Glass Core Substrate</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>T_MLCC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>AI Server MLCC Demand</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -21547,24 +24249,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -21573,24 +24275,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -21599,17 +24301,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -21625,17 +24327,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -21651,17 +24353,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZDT</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zhen Ding Technology</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -21677,102 +24379,102 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ZDT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Zhen Ding Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -21781,17 +24483,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -21807,24 +24509,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -21833,24 +24535,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -21859,24 +24561,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>4</v>
@@ -21885,24 +24587,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
         <v>4</v>
@@ -21911,17 +24613,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -21937,24 +24639,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>4</v>
@@ -21963,128 +24665,128 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -22093,24 +24795,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -22119,17 +24821,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -22145,24 +24847,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -22171,24 +24873,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -22197,17 +24899,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -22223,17 +24925,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -22249,24 +24951,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -22275,17 +24977,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -22301,24 +25003,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -22327,24 +25029,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -22353,12 +25055,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -22379,24 +25081,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
         <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>3</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -22405,17 +25107,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -22431,17 +25133,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -22457,17 +25159,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -22483,24 +25185,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CAMBRICON</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cambricon</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
@@ -22509,90 +25211,90 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>CAMBRICON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Cambricon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>SINOCERA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Sinocera</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -22601,76 +25303,76 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>CHROMA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Chroma ATE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>T_PCB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>AI PCB &amp; CCL Demand</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -22691,17 +25393,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -22717,12 +25419,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -22743,17 +25445,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -22769,17 +25471,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -22795,17 +25497,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -22821,17 +25523,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -22847,17 +25549,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -22873,24 +25575,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
@@ -22899,17 +25601,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NANYA</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -22925,17 +25627,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -22951,17 +25653,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -22977,24 +25679,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SINOCERA</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sinocera</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>2</v>
@@ -23003,17 +25705,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>INNOLIGHT</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Zhongji Innolight</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -23029,64 +25731,64 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="n">
         <v>0</v>
       </c>
-      <c r="E94" t="n">
-        <v>1</v>
-      </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
         <v>0</v>
       </c>
-      <c r="E95" t="n">
-        <v>1</v>
-      </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>INNOLIGHT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>Zhongji Innolight</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -23095,102 +25797,102 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>SEMCO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>SHENGYI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Shengyi Technology</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>ADVANTEST</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>Advantest</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>BESI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>BE Semiconductor (Besi)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -23199,62 +25901,62 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>IBIDEN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Ibiden</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cipher Mining</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
         <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
@@ -23263,24 +25965,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
         <v>1</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -23289,17 +25991,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SAMBANOVA</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -23315,24 +26017,24 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BYTEDANCE</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
         <v>0</v>
-      </c>
-      <c r="E105" t="n">
-        <v>1</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -23341,17 +26043,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LARGAN</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Largan Precision</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -23367,17 +26069,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>WIWYNN</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wiwynn</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -23393,12 +26095,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>XLIGHT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Camtek</t>
+          <t>XLight</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -23419,24 +26121,24 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Naver</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
         <v>0</v>
-      </c>
-      <c r="E109" t="n">
-        <v>1</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
@@ -23445,24 +26147,24 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DOOSAN</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Doosan</t>
+          <t>Cipher Mining</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
         <v>0</v>
-      </c>
-      <c r="E110" t="n">
-        <v>1</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -23471,12 +26173,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HITACHI</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -23497,17 +26199,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KIOXIA</t>
+          <t>SAMBANOVA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kioxia Holdings</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -23523,17 +26225,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ALLSPACE</t>
+          <t>BYTEDANCE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ALL.SPACE</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -23549,17 +26251,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HANMI</t>
+          <t>LARGAN</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hanmi Semiconductor</t>
+          <t>Largan Precision</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -23575,17 +26277,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>WIWYNN</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Wiwynn</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -23601,12 +26303,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>CAMT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FormFactor</t>
+          <t>Camtek</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -23627,24 +26329,24 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Naver</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
         <v>1</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -23653,12 +26355,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IFX</t>
+          <t>DOOSAN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Doosan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -23667,10 +26369,10 @@
         </is>
       </c>
       <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
         <v>1</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -23679,17 +26381,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>HITACHI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -23705,17 +26407,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ENR</t>
+          <t>KIOXIA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Kioxia Holdings</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -23731,24 +26433,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DELTA</t>
+          <t>ALLSPACE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Delta Electronics</t>
+          <t>ALL.SPACE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
         <v>1</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -23757,17 +26459,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ASE</t>
+          <t>HANMI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ASE Technology</t>
+          <t>Hanmi Semiconductor</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -23783,12 +26485,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FOCI</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FOCI</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -23809,17 +26511,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>FormFactor</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -23835,17 +26537,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -23861,12 +26563,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>WOLF</t>
+          <t>IFX</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Wolfspeed</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -23887,17 +26589,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Navitas Semiconductor</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -23913,24 +26615,24 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ENR</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
         <v>0</v>
-      </c>
-      <c r="E128" t="n">
-        <v>1</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -23939,17 +26641,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TSEM</t>
+          <t>DELTA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tower Semiconductor</t>
+          <t>Delta Electronics</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -23959,6 +26661,500 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ASE</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ASE Technology</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>FOCI</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Seagate Technology</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Memory (HBM/DRAM)</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WOLF</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Wolfspeed</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Navitas Semiconductor</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Tower Semiconductor</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Foundry / Manufacturing</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>QUANTA</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Quanta Computer</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>WISTRON</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Wistron</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Networking Systems</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NRG Energy</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Power Generation / Utilities</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>EMC</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Elite Material</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>UNIMICRON</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Unimicron</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>onsemi</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>TeraWulf</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Datacenter Infrastructure (REITs)</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MURATA</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Murata Manufacturing</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TAIYOYUDEN</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Taiyo Yuden</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AI-Supply-Chain-Network.xlsx
+++ b/AI-Supply-Chain-Network.xlsx
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -7955,6 +7955,552 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="inlineStr">
+        <is>
+          <t>Talen Energy</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="F149" s="15" t="inlineStr">
+        <is>
+          <t>Power Generation / Utilities</t>
+        </is>
+      </c>
+      <c r="G149" s="15" t="inlineStr">
+        <is>
+          <t>Independent power producer (IPP)</t>
+        </is>
+      </c>
+      <c r="H149" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I149" s="15" t="inlineStr">
+        <is>
+          <t>Nuclear + gas merchant generation (PJM)</t>
+        </is>
+      </c>
+      <c r="J149" s="15" t="inlineStr">
+        <is>
+          <t>Merchant power producer with AWS nuclear PPA; levered to tightening PJM data-center power market</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B150" s="15" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F150" s="15" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="G150" s="15" t="inlineStr">
+        <is>
+          <t>EMS / contract manufacturing</t>
+        </is>
+      </c>
+      <c r="H150" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>AI server &amp; infrastructure manufacturing</t>
+        </is>
+      </c>
+      <c r="J150" s="15" t="inlineStr">
+        <is>
+          <t>Contract manufacturer ramping AI hardware for hyperscalers</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>RXT</t>
+        </is>
+      </c>
+      <c r="B151" s="15" t="inlineStr">
+        <is>
+          <t>Rackspace Technology</t>
+        </is>
+      </c>
+      <c r="C151" s="15" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>RXT</t>
+        </is>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F151" s="15" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="G151" s="15" t="inlineStr">
+        <is>
+          <t>Managed cloud / neocloud</t>
+        </is>
+      </c>
+      <c r="H151" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>Managed multicloud, AI inference hosting</t>
+        </is>
+      </c>
+      <c r="J151" s="15" t="inlineStr">
+        <is>
+          <t>Cloud operator deploying AMD AI compute capacity for customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>HYGON</t>
+        </is>
+      </c>
+      <c r="B152" s="15" t="inlineStr">
+        <is>
+          <t>Hygon</t>
+        </is>
+      </c>
+      <c r="C152" s="15" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>688041.SS</t>
+        </is>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F152" s="15" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G152" s="15" t="inlineStr">
+        <is>
+          <t>x86 CPU / DCU accelerators</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I152" s="15" t="inlineStr">
+        <is>
+          <t>x86 server CPUs &amp; DCU AI accelerators</t>
+        </is>
+      </c>
+      <c r="J152" s="15" t="inlineStr">
+        <is>
+          <t>China's leading x86 server-CPU and DCU AI-accelerator designer</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>T_CPU</t>
+        </is>
+      </c>
+      <c r="B153" s="15" t="inlineStr">
+        <is>
+          <t>Server CPU &amp; Agentic AI Demand</t>
+        </is>
+      </c>
+      <c r="C153" s="15" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="n"/>
+      <c r="E153" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="15" t="inlineStr">
+        <is>
+          <t>Demand Driver / Theme</t>
+        </is>
+      </c>
+      <c r="G153" s="15" t="inlineStr">
+        <is>
+          <t>Demand driver</t>
+        </is>
+      </c>
+      <c r="H153" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>Server-CPU TAM expansion</t>
+        </is>
+      </c>
+      <c r="J153" s="15" t="inlineStr">
+        <is>
+          <t>Agentic AI shifts CPU:GPU ratio toward 1:1, expanding server-CPU TAM to ~$223bn by 2030 (Bernstein)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>SK Telecom</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>SKM</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>Regional / sovereign AI cloud</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="inlineStr">
+        <is>
+          <t>Gigawatt-scale NVIDIA DSX AI Cloud (Korea)</t>
+        </is>
+      </c>
+      <c r="J154" s="8" t="inlineStr">
+        <is>
+          <t>Telco building NVIDIA-based sovereign AI compute capacity in Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>NITTOBO</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>Nittobo (Nitto Boseki)</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>3110.T</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>Glass cloth / CCL material</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>T-glass &amp; NER-glass cloth for high-end CCL (M8/M9)</t>
+        </is>
+      </c>
+      <c r="J155" s="8" t="inlineStr">
+        <is>
+          <t>High-end glass-cloth supplier; tight supply for AI PCB/CCL substrates</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>JX</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>JX Advanced Metals</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>5016.T</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Interconnect</t>
+        </is>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>Compound-semi substrate material</t>
+        </is>
+      </c>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I156" s="8" t="inlineStr">
+        <is>
+          <t>InP (indium phosphide) substrates for optical transceivers</t>
+        </is>
+      </c>
+      <c r="J156" s="8" t="inlineStr">
+        <is>
+          <t>~40% global InP substrate share; key optical-chip material, capacity expanding 7-10x</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>ALCHIP</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>Alchip Technologies</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>3661.TW</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>Chip Designers (Accelerators/Networking)</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>ASIC design service</t>
+        </is>
+      </c>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I157" s="8" t="inlineStr">
+        <is>
+          <t>Backend/SoC design services for hyperscaler XPUs (AWS Trainium)</t>
+        </is>
+      </c>
+      <c r="J157" s="8" t="inlineStr">
+        <is>
+          <t>ASIC design-service house for custom AI silicon</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>DEEPSEEK</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>AI Labs / Model Developers</t>
+        </is>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>AI lab (China)</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I158" s="8" t="inlineStr">
+        <is>
+          <t>Open-weight frontier LLMs (V-series / R-series)</t>
+        </is>
+      </c>
+      <c r="J158" s="8" t="inlineStr">
+        <is>
+          <t>Chinese frontier-model developer; market-clearing price setter driving indigenous compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>ZHIPU</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>Zhipu AI</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>2513.HK</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>AI Labs / Model Developers</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>AI lab (China)</t>
+        </is>
+      </c>
+      <c r="H159" s="8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I159" s="8" t="inlineStr">
+        <is>
+          <t>GLM frontier model family (GLM-5.x)</t>
+        </is>
+      </c>
+      <c r="J159" s="8" t="inlineStr">
+        <is>
+          <t>Listed Chinese frontier-model developer (GLM)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J48"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -7969,7 +8515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I349"/>
+  <dimension ref="A1:I394"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -9245,12 +9791,12 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>(FACT, X-scan 2026-06-05): Jensen certified SK Hynix for Vera Rubin HBM4 supply (est 60-70% of volume); press-corroborated; lead HBM supplier ; HBM4 full-production cert, ~60-70% allocation (FACT, X-scan 2026-06-12)</t>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified SK Hynix for Vera Rubin HBM4 supply (est 60-70% of volume); press-corroborated; lead HBM supplier ; HBM4 full-production cert, ~60-70% allocation (FACT, X-scan 2026-06-12) | (FACT, X-scan 2026-06-20): NVDA requested 16-Hi HBM4 for H2'26; SK Hynix shipped 12-layer HBM4E samples Jun 18 — NVDA sole HBM4E requester, for Rubin Ultra (384GB/GPU = 8x 48GB) | (FACT, X-scan 2026-06-22): shipped 12-layer HBM4E samples Jun 18 ahead of schedule; NVIDIA sole party currently requesting HBM4E</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
@@ -10322,7 +10868,7 @@
       </c>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>Supermicro builds NVIDIA HGX/GB200 AI servers (FACT, industry/GB200 supply chain 2026)</t>
+          <t>Supermicro builds NVIDIA HGX/GB200 AI servers (FACT, industry/GB200 supply chain 2026) | (FACT, X-scan 2026-06-22): SMCI named global system builder for NVIDIA Vera Rubin NVL4 racks (ISC 2026)</t>
         </is>
       </c>
       <c r="H55" s="15" t="inlineStr">
@@ -10363,15 +10909,23 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="15" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-22): Dell named a builder of NVIDIA Vera Rubin (NVL4) systems at ISC 2026</t>
+        </is>
+      </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I56" s="15" t="n"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-22-2004-x-scan.md</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="9">
       <c r="A57" s="15" t="inlineStr">
@@ -11767,15 +12321,19 @@
       </c>
       <c r="G92" s="15" t="inlineStr">
         <is>
-          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply | (VIEW, UBS 2026-06-09): memory revs +318% YoY '26; DRAM tight/undersupplied under LTA</t>
+          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply | (VIEW, UBS 2026-06-09): memory revs +318% YoY '26; DRAM tight/undersupplied under LTA | (FACT, X-scan 2026-06-20): shipped 12-layer HBM4E samples (48GB/stack, ~16Gbps/pin, ~4TB/s, &gt;20% eff.) ~Jun 18, ahead of prior 2H schedule | (FACT, X-scan 2026-06-22): 12-layer HBM4E sampling (48GB/stack, ~16Gbps/pin) Jun 18 — concrete demand-pull</t>
         </is>
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I92" s="15" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-20-1204-x-scan.md</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="9">
       <c r="A93" s="15" t="inlineStr">
@@ -11808,15 +12366,19 @@
       </c>
       <c r="G93" s="15" t="inlineStr">
         <is>
-          <t>None | (FACT, X-scan 2026-06-11): entire 2026 HBM capacity booked/sold out under binding contracts; HBM4 stack shown at COMPUTEX 2026 | (VIEW, UBS 2026-06-09): structural memory shortage; DRAM/NAND tight under LTA; PT $1,625</t>
+          <t>None | (FACT, X-scan 2026-06-11): entire 2026 HBM capacity booked/sold out under binding contracts; HBM4 stack shown at COMPUTEX 2026 | (VIEW, UBS 2026-06-09): structural memory shortage; DRAM/NAND tight under LTA; PT $1,625 | (FACT, X-scan 2026-06-20): top-3 HBM maker; HBM4 demand driving record results into FQ3 (Jun 24 earnings)</t>
         </is>
       </c>
       <c r="H93" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I93" s="15" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-20-0404-x-scan.md</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="9">
       <c r="A94" s="15" t="inlineStr">
@@ -11849,15 +12411,19 @@
       </c>
       <c r="G94" s="15" t="inlineStr">
         <is>
-          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply | (VIEW, UBS 2026-06-09): memory undersupplied through '27; DRAM-led WFE buildout</t>
+          <t>(VIEW, GS/Morgan Stanley 2026-06): HBM/DRAM undersupplied through 2028; shortage drives pricing power, 3Q ASP +20%+, LTAs signal tight supply | (VIEW, UBS 2026-06-09): memory undersupplied through '27; DRAM-led WFE buildout | (FACT, X-scan 2026-06-20): HBM4E samples sent May 29; scaling HBM capacity ~50% in 2026, re-entering HBM4 supply</t>
         </is>
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I94" s="15" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-20-1204-x-scan.md</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="9">
       <c r="A95" s="15" t="inlineStr">
@@ -17655,12 +18221,12 @@
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>(FACT, X-scan 2026-06-05): Jensen certified Micron for Vera Rubin HBM4 supply; press-corroborated ; HBM4 full-production cert, remainder of allocation (FACT, X-scan 2026-06-12)</t>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified Micron for Vera Rubin HBM4 supply; press-corroborated ; HBM4 full-production cert, remainder of allocation (FACT, X-scan 2026-06-12) | (FACT, X-scan 2026-06-20): NVDA requested 16-Hi HBM4 for H2'26 (Q4 delivery); Micron met Rubin HBM4 spec &amp; delivered final customer samples; expanding HBM4 wafer capacity into end-2026</t>
         </is>
       </c>
       <c r="H230" s="8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I230" s="8" t="inlineStr">
@@ -17700,12 +18266,12 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>(FACT, X-scan 2026-06-05): Jensen certified Samsung for Vera Rubin HBM4 supply; press-corroborated ; HBM4 full-production cert, ~25-30% allocation (FACT, X-scan 2026-06-12)</t>
+          <t>(FACT, X-scan 2026-06-05): Jensen certified Samsung for Vera Rubin HBM4 supply; press-corroborated ; HBM4 full-production cert, ~25-30% allocation (FACT, X-scan 2026-06-12) | (FACT, X-scan 2026-06-20): NVDA requested 16-Hi HBM4 for H2'26; Samsung re-engaged on HBM4</t>
         </is>
       </c>
       <c r="H231" s="8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I231" s="8" t="inlineStr">
@@ -23021,6 +23587,2031 @@
       <c r="I349" s="18" t="inlineStr">
         <is>
           <t>大摩-电子元器件MLCC.pdf; MS 上调村田 MLCC.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="15" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="B350" s="15" t="inlineStr">
+        <is>
+          <t>Talen Energy</t>
+        </is>
+      </c>
+      <c r="C350" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D350" s="15" t="inlineStr">
+        <is>
+          <t>T_POWER</t>
+        </is>
+      </c>
+      <c r="E350" s="15" t="inlineStr">
+        <is>
+          <t>Datacenter Power Demand</t>
+        </is>
+      </c>
+      <c r="F350" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G350" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Narrative Atlas 2026-06-18): Buy rating; unique leverage to tightening PJM power market from data-center demand; AWS power agreement de-risks cash flows</t>
+        </is>
+      </c>
+      <c r="H350" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I350" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="15" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B351" s="15" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C351" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D351" s="15" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E351" s="15" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F351" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G351" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Narrative Atlas 2026-06-18): PT raised to $470; F3Q beat, new hyperscaler customer win, multi-year AI infrastructure opportunity</t>
+        </is>
+      </c>
+      <c r="H351" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I351" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="15" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B352" s="15" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise</t>
+        </is>
+      </c>
+      <c r="C352" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D352" s="15" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E352" s="15" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F352" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G352" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Barclays 2026-06-17): strong AI-networking demand; ahead-of-schedule Juniper integration embedding AI across products</t>
+        </is>
+      </c>
+      <c r="H352" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I352" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B353" s="15" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C353" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D353" s="15" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E353" s="15" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F353" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G353" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06-17): raised long-term WFE outlook on AI-driven memory build; underappreciated NAND equipment up-cycle</t>
+        </is>
+      </c>
+      <c r="H353" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I353" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="15" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B354" s="15" t="inlineStr">
+        <is>
+          <t>Lam Research</t>
+        </is>
+      </c>
+      <c r="C354" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D354" s="15" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E354" s="15" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F354" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G354" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06-17): raised WFE targets on AI-driven memory/NAND equipment cycle</t>
+        </is>
+      </c>
+      <c r="H354" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I354" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="15" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B355" s="15" t="inlineStr">
+        <is>
+          <t>KLA Corporation</t>
+        </is>
+      </c>
+      <c r="C355" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D355" s="15" t="inlineStr">
+        <is>
+          <t>T_HBM</t>
+        </is>
+      </c>
+      <c r="E355" s="15" t="inlineStr">
+        <is>
+          <t>HBM Demand</t>
+        </is>
+      </c>
+      <c r="F355" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G355" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Citi 2026-06-17): raised WFE targets on AI-driven memory/NAND equipment cycle</t>
+        </is>
+      </c>
+      <c r="H355" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I355" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="15" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B356" s="15" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C356" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D356" s="15" t="inlineStr">
+        <is>
+          <t>T_CPU</t>
+        </is>
+      </c>
+      <c r="E356" s="15" t="inlineStr">
+        <is>
+          <t>Server CPU &amp; Agentic AI Demand</t>
+        </is>
+      </c>
+      <c r="F356" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G356" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06-17): server CPU renaissance from agentic AI; INTC estimates/PT raised to $100; CPU TAM ~$223bn by 2030</t>
+        </is>
+      </c>
+      <c r="H356" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I356" s="15" t="inlineStr">
+        <is>
+          <t>Bernstein-Global Semiconductors Global Semis： The CPU Renaissance？ Beneficiaries of a $223bn TAM...-260617.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="15" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B357" s="15" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C357" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D357" s="15" t="inlineStr">
+        <is>
+          <t>T_CPU</t>
+        </is>
+      </c>
+      <c r="E357" s="15" t="inlineStr">
+        <is>
+          <t>Server CPU &amp; Agentic AI Demand</t>
+        </is>
+      </c>
+      <c r="F357" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G357" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06-17): agentic AI lifts server CPU demand; AMD share-gain trajectory; PT $600</t>
+        </is>
+      </c>
+      <c r="H357" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I357" s="15" t="inlineStr">
+        <is>
+          <t>Bernstein-Global Semiconductors Global Semis： The CPU Renaissance？ Beneficiaries of a $223bn TAM...-260617.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="15" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B358" s="15" t="inlineStr">
+        <is>
+          <t>Arm Holdings</t>
+        </is>
+      </c>
+      <c r="C358" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D358" s="15" t="inlineStr">
+        <is>
+          <t>T_CPU</t>
+        </is>
+      </c>
+      <c r="E358" s="15" t="inlineStr">
+        <is>
+          <t>Server CPU &amp; Agentic AI Demand</t>
+        </is>
+      </c>
+      <c r="F358" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G358" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06-17): Arm structural beneficiary of CPU renaissance; unparalleled power efficiency; PT $500</t>
+        </is>
+      </c>
+      <c r="H358" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I358" s="15" t="inlineStr">
+        <is>
+          <t>Bernstein-Global Semiconductors Global Semis： The CPU Renaissance？ Beneficiaries of a $223bn TAM...-260617.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="15" t="inlineStr">
+        <is>
+          <t>HYGON</t>
+        </is>
+      </c>
+      <c r="B359" s="15" t="inlineStr">
+        <is>
+          <t>Hygon</t>
+        </is>
+      </c>
+      <c r="C359" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D359" s="15" t="inlineStr">
+        <is>
+          <t>T_CPU</t>
+        </is>
+      </c>
+      <c r="E359" s="15" t="inlineStr">
+        <is>
+          <t>Server CPU &amp; Agentic AI Demand</t>
+        </is>
+      </c>
+      <c r="F359" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G359" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06-17): set to benefit from strong x86 server-CPU demand and gain China share</t>
+        </is>
+      </c>
+      <c r="H359" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I359" s="15" t="inlineStr">
+        <is>
+          <t>Bernstein-Global Semiconductors Global Semis： The CPU Renaissance？ Beneficiaries of a $223bn TAM...-260617.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="15" t="inlineStr">
+        <is>
+          <t>HYGON</t>
+        </is>
+      </c>
+      <c r="B360" s="15" t="inlineStr">
+        <is>
+          <t>Hygon</t>
+        </is>
+      </c>
+      <c r="C360" s="15" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D360" s="15" t="inlineStr">
+        <is>
+          <t>T_CHINA</t>
+        </is>
+      </c>
+      <c r="E360" s="15" t="inlineStr">
+        <is>
+          <t>China Indigenous AI Buildout</t>
+        </is>
+      </c>
+      <c r="F360" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G360" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Bernstein 2026-06-17): China to outpace global x86 growth from 2028 as advanced-node constraints ease; AI investment unlocks CPU potential</t>
+        </is>
+      </c>
+      <c r="H360" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I360" s="15" t="inlineStr">
+        <is>
+          <t>Bernstein-Global Semiconductors Global Semis： The CPU Renaissance？ Beneficiaries of a $223bn TAM...-260617.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="15" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B361" s="15" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C361" s="15" t="inlineStr">
+        <is>
+          <t>manufactures chips for</t>
+        </is>
+      </c>
+      <c r="D361" s="15" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E361" s="15" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F361" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" s="15" t="inlineStr">
+        <is>
+          <t>(VIEW, Narrative Atlas 2026-06-18): Trump says Intel working to design Apple chips; rumored/unconfirmed (?)</t>
+        </is>
+      </c>
+      <c r="H361" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I361" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="15" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B362" s="15" t="inlineStr">
+        <is>
+          <t>SpaceX (Colossus compute)</t>
+        </is>
+      </c>
+      <c r="C362" s="15" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D362" s="15" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E362" s="15" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="F362" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G362" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, Narrative Atlas 2026-06-16): Alphabet/Google leasing cloud computing capacity to SpaceX</t>
+        </is>
+      </c>
+      <c r="H362" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="I362" s="15" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="15" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B363" s="15" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="C363" s="15" t="inlineStr">
+        <is>
+          <t>manufactures chips for</t>
+        </is>
+      </c>
+      <c r="D363" s="15" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="E363" s="15" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="F363" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G363" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-18): Micron to outsource HBM4E base-die production to TSMC (mass production targeted 2027)</t>
+        </is>
+      </c>
+      <c r="H363" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I363" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18-0404-x-scan-extract.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="15" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B364" s="15" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C364" s="15" t="inlineStr">
+        <is>
+          <t>sells GPUs to</t>
+        </is>
+      </c>
+      <c r="D364" s="15" t="inlineStr">
+        <is>
+          <t>RXT</t>
+        </is>
+      </c>
+      <c r="E364" s="15" t="inlineStr">
+        <is>
+          <t>Rackspace Technology</t>
+        </is>
+      </c>
+      <c r="F364" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G364" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-18): AMD–Rackspace definitive agreement to deploy 30MW of AMD AI compute across Rackspace datacenters, 2026-2028</t>
+        </is>
+      </c>
+      <c r="H364" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I364" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18-0404-x-scan-extract.md; 2026-06-18-1204-x-scan-extract.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="15" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B365" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C365" s="15" t="inlineStr">
+        <is>
+          <t>provides datacenter capacity to</t>
+        </is>
+      </c>
+      <c r="D365" s="15" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="E365" s="15" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="F365" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G365" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, CoreWeave/Key Context 2026-06-17): CoreWeave names OpenAI among its independent-cloud customers</t>
+        </is>
+      </c>
+      <c r="H365" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I365" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave 高管访谈：AI 需求似乎每天都在“加剧” --- An Interview with CoreWeave Executives AI Demand Seems to 'Intensify' Every Day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B366" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C366" s="15" t="inlineStr">
+        <is>
+          <t>provides datacenter capacity to</t>
+        </is>
+      </c>
+      <c r="D366" s="15" t="inlineStr">
+        <is>
+          <t>ANTHROPIC</t>
+        </is>
+      </c>
+      <c r="E366" s="15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="F366" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G366" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, CoreWeave/Key Context 2026-06-17): CoreWeave names Anthropic as a customer</t>
+        </is>
+      </c>
+      <c r="H366" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I366" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave 高管访谈：AI 需求似乎每天都在“加剧” --- An Interview with CoreWeave Executives AI Demand Seems to 'Intensify' Every Day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="15" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B367" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C367" s="15" t="inlineStr">
+        <is>
+          <t>provides datacenter capacity to</t>
+        </is>
+      </c>
+      <c r="D367" s="15" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E367" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F367" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G367" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, CoreWeave/Key Context 2026-06-17): CoreWeave names Microsoft as a customer</t>
+        </is>
+      </c>
+      <c r="H367" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I367" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave 高管访谈：AI 需求似乎每天都在“加剧” --- An Interview with CoreWeave Executives AI Demand Seems to 'Intensify' Every Day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="15" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B368" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C368" s="15" t="inlineStr">
+        <is>
+          <t>provides datacenter capacity to</t>
+        </is>
+      </c>
+      <c r="D368" s="15" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="E368" s="15" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="F368" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G368" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, CoreWeave/Key Context 2026-06-17): CoreWeave names Meta as a customer</t>
+        </is>
+      </c>
+      <c r="H368" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I368" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave 高管访谈：AI 需求似乎每天都在“加剧” --- An Interview with CoreWeave Executives AI Demand Seems to 'Intensify' Every Day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="15" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B369" s="15" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C369" s="15" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D369" s="15" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E369" s="15" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F369" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G369" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, JPM 2026-06-16): Broadcom XPU pipeline includes an Apple AI CPU program</t>
+        </is>
+      </c>
+      <c r="H369" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="I369" s="15" t="inlineStr">
+        <is>
+          <t>JPM_Broadcom_Inc_Ignore__2026-06-17_5337309.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="15" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B370" s="15" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C370" s="15" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D370" s="15" t="inlineStr">
+        <is>
+          <t>SAMBANOVA</t>
+        </is>
+      </c>
+      <c r="E370" s="15" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="F370" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G370" s="15" t="inlineStr">
+        <is>
+          <t>(FACT, JPM 2026-06-16): Broadcom ASIC pipeline includes SambaNova RDU program</t>
+        </is>
+      </c>
+      <c r="H370" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="I370" s="15" t="inlineStr">
+        <is>
+          <t>JPM_Broadcom_Inc_Ignore__2026-06-17_5337309.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B371" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C371" s="8" t="inlineStr">
+        <is>
+          <t>sells GPUs to</t>
+        </is>
+      </c>
+      <c r="D371" s="8" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="E371" s="8" t="inlineStr">
+        <is>
+          <t>SK Telecom</t>
+        </is>
+      </c>
+      <c r="F371" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G371" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-21): SK Telecom to build gigawatt-scale AI Cloud in Korea on NVIDIA DSX platform, announced Jun 18 2026</t>
+        </is>
+      </c>
+      <c r="H371" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="I371" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21-1204-x-scan-extract.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="8" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B372" s="8" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C372" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D372" s="8" t="inlineStr">
+        <is>
+          <t>T_GLASS</t>
+        </is>
+      </c>
+      <c r="E372" s="8" t="inlineStr">
+        <is>
+          <t>Glass Core Substrate</t>
+        </is>
+      </c>
+      <c r="F372" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G372" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Expert call 2026-06-17): Samsung most aggressive in glass-core substrate; sent samples to NVIDIA/Broadcom; Apple to source for AI servers</t>
+        </is>
+      </c>
+      <c r="H372" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I372" s="8" t="inlineStr">
+        <is>
+          <t>玻璃基板纪要_20260617_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="8" t="inlineStr">
+        <is>
+          <t>SEMCO</t>
+        </is>
+      </c>
+      <c r="B373" s="8" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="C373" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D373" s="8" t="inlineStr">
+        <is>
+          <t>T_GLASS</t>
+        </is>
+      </c>
+      <c r="E373" s="8" t="inlineStr">
+        <is>
+          <t>Glass Core Substrate</t>
+        </is>
+      </c>
+      <c r="F373" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G373" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Expert call 2026-06-20): Samsung Electro-Mechanics developing glass substrate, progressing well</t>
+        </is>
+      </c>
+      <c r="H373" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="I373" s="8" t="inlineStr">
+        <is>
+          <t>玻璃基板TGV专家交流纪要_20260620_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="8" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B374" s="8" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="C374" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D374" s="8" t="inlineStr">
+        <is>
+          <t>T_GLASS</t>
+        </is>
+      </c>
+      <c r="E374" s="8" t="inlineStr">
+        <is>
+          <t>Glass Core Substrate</t>
+        </is>
+      </c>
+      <c r="F374" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G374" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Expert call 2026-06-17): TSMC released glass-substrate dev plan, pilot line Jun 2026, ~2027-28 mass production to replace silicon interposer in CoWoS</t>
+        </is>
+      </c>
+      <c r="H374" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I374" s="8" t="inlineStr">
+        <is>
+          <t>玻璃基板纪要_20260617_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="8" t="inlineStr">
+        <is>
+          <t>NITTOBO</t>
+        </is>
+      </c>
+      <c r="B375" s="8" t="inlineStr">
+        <is>
+          <t>Nittobo (Nitto Boseki)</t>
+        </is>
+      </c>
+      <c r="C375" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D375" s="8" t="inlineStr">
+        <is>
+          <t>T_PCB</t>
+        </is>
+      </c>
+      <c r="E375" s="8" t="inlineStr">
+        <is>
+          <t>AI PCB &amp; CCL Demand</t>
+        </is>
+      </c>
+      <c r="F375" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G375" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, JPM 2026-06-15): supplies high-quality T-glass/NER-glass cloth for M8/M9 CCL; demand exceeds supply, tight, stable-supply advantage; competitors Taiwan Glass, Unitika, Nanya Plastics</t>
+        </is>
+      </c>
+      <c r="H375" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I375" s="8" t="inlineStr">
+        <is>
+          <t>JPM-日东纺(Nittobo, 3110.T)：上调盈利预测——T-glass厚核（Thick Cores）与NER-glass切入M9等级带来增量机遇.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="8" t="inlineStr">
+        <is>
+          <t>JX</t>
+        </is>
+      </c>
+      <c r="B376" s="8" t="inlineStr">
+        <is>
+          <t>JX Advanced Metals</t>
+        </is>
+      </c>
+      <c r="C376" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D376" s="8" t="inlineStr">
+        <is>
+          <t>T_NET</t>
+        </is>
+      </c>
+      <c r="E376" s="8" t="inlineStr">
+        <is>
+          <t>Optical &amp; Networking Buildout</t>
+        </is>
+      </c>
+      <c r="F376" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G376" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Nomura 2026-06-16): ~40% global InP substrate share for optical transceivers; tight supply / undersupplied; China export controls lifted prices 2-3x; plans 7-10x capacity expansion</t>
+        </is>
+      </c>
+      <c r="H376" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="I376" s="8" t="inlineStr">
+        <is>
+          <t>Nomura-JX Advanced Metals（5016.T）——日经报道拟将磷化铟（InP）衬底产能最高扩至10倍.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="8" t="inlineStr">
+        <is>
+          <t>JX</t>
+        </is>
+      </c>
+      <c r="B377" s="8" t="inlineStr">
+        <is>
+          <t>JX Advanced Metals</t>
+        </is>
+      </c>
+      <c r="C377" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D377" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E377" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F377" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G377" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Nomura 2026-06-16): InP substrate is upstream material for optical/CPO devices; datacenter optical demand strong</t>
+        </is>
+      </c>
+      <c r="H377" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="I377" s="8" t="inlineStr">
+        <is>
+          <t>Nomura-JX Advanced Metals（5016.T）——日经报道拟将磷化铟（InP）衬底产能最高扩至10倍.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="8" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B378" s="8" t="inlineStr">
+        <is>
+          <t>Marvell</t>
+        </is>
+      </c>
+      <c r="C378" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D378" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="E378" s="8" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F378" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G378" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, JPM 2026-06): Marvell co-designs AWS Trainium 3 XPU (alongside Alchip)</t>
+        </is>
+      </c>
+      <c r="H378" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I378" s="8" t="inlineStr">
+        <is>
+          <t>AI Drives Resurgence in Custom Chips (ASICs) ASIC Market OverviewUpdate.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="8" t="inlineStr">
+        <is>
+          <t>ALCHIP</t>
+        </is>
+      </c>
+      <c r="B379" s="8" t="inlineStr">
+        <is>
+          <t>Alchip Technologies</t>
+        </is>
+      </c>
+      <c r="C379" s="8" t="inlineStr">
+        <is>
+          <t>co-designs custom silicon with</t>
+        </is>
+      </c>
+      <c r="D379" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="E379" s="8" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F379" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G379" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, JPM 2026-06): Alchip provides design services for AWS Trainium 3</t>
+        </is>
+      </c>
+      <c r="H379" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I379" s="8" t="inlineStr">
+        <is>
+          <t>AI Drives Resurgence in Custom Chips (ASICs) ASIC Market OverviewUpdate.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="8" t="inlineStr">
+        <is>
+          <t>ALCHIP</t>
+        </is>
+      </c>
+      <c r="B380" s="8" t="inlineStr">
+        <is>
+          <t>Alchip Technologies</t>
+        </is>
+      </c>
+      <c r="C380" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D380" s="8" t="inlineStr">
+        <is>
+          <t>T_TRAIN</t>
+        </is>
+      </c>
+      <c r="E380" s="8" t="inlineStr">
+        <is>
+          <t>AI Training Capex</t>
+        </is>
+      </c>
+      <c r="F380" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G380" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): ASIC resurgence; custom XPU unit shipments forecast to exceed GPU units by 2027</t>
+        </is>
+      </c>
+      <c r="H380" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="I380" s="8" t="inlineStr">
+        <is>
+          <t>AI Drives Resurgence in Custom Chips (ASICs) ASIC Market OverviewUpdate.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="8" t="inlineStr">
+        <is>
+          <t>ADVANTEST</t>
+        </is>
+      </c>
+      <c r="B381" s="8" t="inlineStr">
+        <is>
+          <t>Advantest</t>
+        </is>
+      </c>
+      <c r="C381" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D381" s="8" t="inlineStr">
+        <is>
+          <t>T_CPU</t>
+        </is>
+      </c>
+      <c r="E381" s="8" t="inlineStr">
+        <is>
+          <t>Server CPU &amp; Agentic AI Demand</t>
+        </is>
+      </c>
+      <c r="F381" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G381" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): raising estimates on new server-CPU test demand beyond GPU/ASIC</t>
+        </is>
+      </c>
+      <c r="H381" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I381" s="8" t="inlineStr">
+        <is>
+          <t>JPM-爱德万测试（6857.T）——上调盈利预测：GPUASIC之外新增CPUCPO需求预期.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="8" t="inlineStr">
+        <is>
+          <t>ADVANTEST</t>
+        </is>
+      </c>
+      <c r="B382" s="8" t="inlineStr">
+        <is>
+          <t>Advantest</t>
+        </is>
+      </c>
+      <c r="C382" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D382" s="8" t="inlineStr">
+        <is>
+          <t>T_CPO</t>
+        </is>
+      </c>
+      <c r="E382" s="8" t="inlineStr">
+        <is>
+          <t>Co-Packaged Optics (CPO)</t>
+        </is>
+      </c>
+      <c r="F382" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G382" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06): new CPO test demand incremental to GPU/ASIC</t>
+        </is>
+      </c>
+      <c r="H382" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I382" s="8" t="inlineStr">
+        <is>
+          <t>JPM-爱德万测试（6857.T）——上调盈利预测：GPUASIC之外新增CPUCPO需求预期.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B383" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C383" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D383" s="8" t="inlineStr">
+        <is>
+          <t>T_CPU</t>
+        </is>
+      </c>
+      <c r="E383" s="8" t="inlineStr">
+        <is>
+          <t>Server CPU &amp; Agentic AI Demand</t>
+        </is>
+      </c>
+      <c r="F383" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G383" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Expert call 2026-06-18): NVIDIA Vera (88-core Arm data-center CPU); Rubin rack decouples CPU/GPU scaling over NVLink</t>
+        </is>
+      </c>
+      <c r="H383" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I383" s="8" t="inlineStr">
+        <is>
+          <t>CPU专家电话会纪要_20260618.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="8" t="inlineStr">
+        <is>
+          <t>DEEPSEEK</t>
+        </is>
+      </c>
+      <c r="B384" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="C384" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D384" s="8" t="inlineStr">
+        <is>
+          <t>T_CHINA</t>
+        </is>
+      </c>
+      <c r="E384" s="8" t="inlineStr">
+        <is>
+          <t>China Indigenous AI Buildout</t>
+        </is>
+      </c>
+      <c r="F384" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G384" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Expert call 2026-06): central to China indigenous AI; targets &gt;=50% domestic share post full-localization</t>
+        </is>
+      </c>
+      <c r="H384" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="I384" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek商业化与下一代模型储备纪要_20260621_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="8" t="inlineStr">
+        <is>
+          <t>DEEPSEEK</t>
+        </is>
+      </c>
+      <c r="B385" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="C385" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D385" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E385" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F385" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G385" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Expert call 2026-06): inference-driven model monetization; sets market-clearing price for good-enough intelligence</t>
+        </is>
+      </c>
+      <c r="H385" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="I385" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek商业化与下一代模型储备纪要_20260621_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="8" t="inlineStr">
+        <is>
+          <t>DEEPSEEK</t>
+        </is>
+      </c>
+      <c r="B386" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="C386" s="8" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D386" s="8" t="inlineStr">
+        <is>
+          <t>HUAWEI</t>
+        </is>
+      </c>
+      <c r="E386" s="8" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="F386" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G386" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Expert call 2026-06): completed inference adaptation on Huawei Ascend 950PR</t>
+        </is>
+      </c>
+      <c r="H386" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="I386" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek商业化与下一代模型储备纪要_20260621_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="8" t="inlineStr">
+        <is>
+          <t>DEEPSEEK</t>
+        </is>
+      </c>
+      <c r="B387" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="C387" s="8" t="inlineStr">
+        <is>
+          <t>runs compute on</t>
+        </is>
+      </c>
+      <c r="D387" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E387" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F387" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G387" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, Expert call 2026-06): training still primarily on NVIDIA GPUs (CANN ecosystem immature)</t>
+        </is>
+      </c>
+      <c r="H387" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="I387" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek商业化与下一代模型储备纪要_20260621_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="8" t="inlineStr">
+        <is>
+          <t>DEEPSEEK</t>
+        </is>
+      </c>
+      <c r="B388" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="C388" s="8" t="inlineStr">
+        <is>
+          <t>competes with</t>
+        </is>
+      </c>
+      <c r="D388" s="8" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="E388" s="8" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="F388" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G388" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM/Expert 2026-06): price competition; pulls down market-clearing price vs OpenAI/Anthropic</t>
+        </is>
+      </c>
+      <c r="H388" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="I388" s="8" t="inlineStr">
+        <is>
+          <t>DeepSeek商业化与下一代模型储备纪要_20260621_已核实.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="8" t="inlineStr">
+        <is>
+          <t>ZHIPU</t>
+        </is>
+      </c>
+      <c r="B389" s="8" t="inlineStr">
+        <is>
+          <t>Zhipu AI</t>
+        </is>
+      </c>
+      <c r="C389" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D389" s="8" t="inlineStr">
+        <is>
+          <t>T_CHINA</t>
+        </is>
+      </c>
+      <c r="E389" s="8" t="inlineStr">
+        <is>
+          <t>China Indigenous AI Buildout</t>
+        </is>
+      </c>
+      <c r="F389" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G389" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06-18): frontier model capability in China; GLM-5.2 upgrade</t>
+        </is>
+      </c>
+      <c r="H389" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I389" s="8" t="inlineStr">
+        <is>
+          <t>智谱.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="8" t="inlineStr">
+        <is>
+          <t>ZHIPU</t>
+        </is>
+      </c>
+      <c r="B390" s="8" t="inlineStr">
+        <is>
+          <t>Zhipu AI</t>
+        </is>
+      </c>
+      <c r="C390" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D390" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E390" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F390" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G390" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, JPM 2026-06-18): model-layer monetization; API pricing visibility (GLM-5.2 +13% blended)</t>
+        </is>
+      </c>
+      <c r="H390" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I390" s="8" t="inlineStr">
+        <is>
+          <t>智谱.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="8" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B391" s="8" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C391" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D391" s="8" t="inlineStr">
+        <is>
+          <t>T_COWOS</t>
+        </is>
+      </c>
+      <c r="E391" s="8" t="inlineStr">
+        <is>
+          <t>CoWoS Advanced Packaging</t>
+        </is>
+      </c>
+      <c r="F391" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G391" s="8" t="inlineStr">
+        <is>
+          <t>(FACT, X-scan 2026-06-22): Lisa Su (Computex) announced &gt;$10B Taiwan investment directed at advanced-packaging capacity for next-gen AI infra</t>
+        </is>
+      </c>
+      <c r="H391" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I391" s="8" t="inlineStr">
+        <is>
+          <t>X-Reports/2026-06-22-1204-x-scan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="8" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B392" s="8" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="C392" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D392" s="8" t="inlineStr">
+        <is>
+          <t>T_INFER</t>
+        </is>
+      </c>
+      <c r="E392" s="8" t="inlineStr">
+        <is>
+          <t>AI Inference Demand</t>
+        </is>
+      </c>
+      <c r="F392" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G392" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Needham 2026-06-22): raised PT/ests; robust AI-driven demand + limited capacity additions extend the memory upcycle, continued DRAM pricing increases</t>
+        </is>
+      </c>
+      <c r="H392" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I392" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="8" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B393" s="8" t="inlineStr">
+        <is>
+          <t>Lam Research</t>
+        </is>
+      </c>
+      <c r="C393" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D393" s="8" t="inlineStr">
+        <is>
+          <t>T_COWOS</t>
+        </is>
+      </c>
+      <c r="E393" s="8" t="inlineStr">
+        <is>
+          <t>CoWoS Advanced Packaging</t>
+        </is>
+      </c>
+      <c r="F393" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G393" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Mizuho 2026-06-22): advanced packaging (Intel EMIB-T/glass) creating incremental demand across the broader semicap ecosystem, particularly Lam</t>
+        </is>
+      </c>
+      <c r="H393" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I393" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="8" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B394" s="8" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C394" s="8" t="inlineStr">
+        <is>
+          <t>benefits from</t>
+        </is>
+      </c>
+      <c r="D394" s="8" t="inlineStr">
+        <is>
+          <t>T_COWOS</t>
+        </is>
+      </c>
+      <c r="E394" s="8" t="inlineStr">
+        <is>
+          <t>CoWoS Advanced Packaging</t>
+        </is>
+      </c>
+      <c r="F394" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G394" s="8" t="inlineStr">
+        <is>
+          <t>(VIEW, Mizuho 2026-06-22): advanced-packaging demand growth creating incremental semicap demand, particularly Applied Materials</t>
+        </is>
+      </c>
+      <c r="H394" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I394" s="8" t="inlineStr">
+        <is>
+          <t>https://narrative-graph.onrender.com/feed</t>
         </is>
       </c>
     </row>
@@ -23301,7 +25892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23353,13 +25944,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -23382,10 +25973,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -23408,10 +25999,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -23434,10 +26025,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -23460,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -23483,13 +26074,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -23512,10 +26103,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -23535,13 +26126,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -23561,13 +26152,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -23590,21 +26181,21 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alphabet (Google)</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23613,24 +26204,24 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet (Google)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -23639,13 +26230,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -23665,13 +26256,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -23694,10 +26285,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -23720,10 +26311,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -23743,13 +26334,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -23769,102 +26360,102 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>T_COWOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>CoWoS Advanced Packaging</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>T_GLASS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Glass Core Substrate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SpaceX (Colossus compute)</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -23873,117 +26464,117 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SKHYNIX</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>SpaceX (Colossus compute)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -24006,21 +26597,21 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>ANTHROPIC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -24032,33 +26623,33 @@
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ANTHROPIC</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>6</v>
@@ -24067,17 +26658,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -24093,24 +26684,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T_COWOS</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CoWoS Advanced Packaging</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>6</v>
@@ -24119,24 +26710,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T_GLASS</t>
+          <t>SKHYNIX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Glass Core Substrate</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
@@ -24145,24 +26736,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>6</v>
@@ -24171,24 +26762,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>6</v>
@@ -24197,24 +26788,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T_MLCC</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AI Server MLCC Demand</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" t="n">
         <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>6</v>
       </c>
       <c r="F35" t="n">
         <v>6</v>
@@ -24223,147 +26814,147 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>T_MLCC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>AI Server MLCC Demand</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>T_CPU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Server CPU &amp; Agentic AI Demand</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -24379,24 +26970,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ILUVATAR</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Iluvatar CoreX</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
@@ -24405,24 +26996,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
@@ -24431,17 +27022,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZDT</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zhen Ding Technology</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -24457,154 +27048,154 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EDA &amp; IP</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ILUVATAR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Iluvatar CoreX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FOXCONN</t>
+          <t>ZDT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Foxconn (Hon Hai)</t>
+          <t>Zhen Ding Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>DEEPSEEK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>EDA &amp; IP</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>4</v>
@@ -24613,17 +27204,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -24639,24 +27230,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AAOI</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Applied Optoelectronics</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
         <v>4</v>
@@ -24665,24 +27256,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>FOXCONN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foxconn (Hon Hai)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>4</v>
@@ -24691,24 +27282,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>4</v>
@@ -24717,24 +27308,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>4</v>
@@ -24743,12 +27334,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -24757,10 +27348,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>4</v>
@@ -24769,199 +27360,199 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AAOI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Applied Optoelectronics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>ADVANTEST</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Advantest</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>T_PCB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>AI PCB &amp; CCL Demand</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -24977,17 +27568,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -25003,24 +27594,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BOE Technology</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -25029,17 +27620,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>INNOLUX</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Innolux</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -25055,24 +27646,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HUAWEI</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
         <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -25081,17 +27672,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -25107,17 +27698,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -25133,24 +27724,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>BOE Technology</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>3</v>
@@ -25159,24 +27750,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SIVE</t>
+          <t>INNOLUX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sivers Semiconductor</t>
+          <t>Innolux</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
@@ -25185,24 +27776,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI Labs / Model Developers</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="n">
         <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
@@ -25211,17 +27802,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AYAR</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ayar Labs</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -25237,17 +27828,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -25263,24 +27854,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAMBRICON</t>
+          <t>SIVE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cambricon</t>
+          <t>Sivers Semiconductor</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>3</v>
@@ -25289,24 +27880,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SINOCERA</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sinocera</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
         <v>3</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>3</v>
@@ -25315,24 +27906,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHROMA</t>
+          <t>AYAR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Chroma ATE</t>
+          <t>Ayar Labs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>3</v>
@@ -25341,24 +27932,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T_PCB</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AI PCB &amp; CCL Demand</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D79" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" t="n">
         <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>3</v>
       </c>
       <c r="F79" t="n">
         <v>3</v>
@@ -25367,38 +27958,38 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FURUKAWA</t>
+          <t>CAMBRICON</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>Cambricon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NAURA</t>
+          <t>SINOCERA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Naura Technology</t>
+          <t>Sinocera</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -25407,88 +27998,88 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AMEC</t>
+          <t>SEMCO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Advanced Micro-Fabrication (AMEC)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>METAX</t>
+          <t>CHROMA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MetaX</t>
+          <t>Chroma ATE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CXMT</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ChangXin Memory (CXMT)</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -25497,12 +28088,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LUXSHARE</t>
+          <t>FURUKAWA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Luxshare Precision</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -25523,17 +28114,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AUO</t>
+          <t>NAURA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>Naura Technology</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -25549,17 +28140,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>AMEC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>Advanced Micro-Fabrication (AMEC)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -25575,17 +28166,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>METAX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>MetaX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -25601,17 +28192,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CXMT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>ChangXin Memory (CXMT)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -25627,17 +28218,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>XFAB</t>
+          <t>LUXSHARE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>X-FAB</t>
+          <t>Luxshare Precision</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -25653,17 +28244,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>POET</t>
+          <t>AUO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>POET Technologies</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -25679,24 +28270,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>2</v>
@@ -25705,17 +28296,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NANYA</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -25731,17 +28322,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -25757,17 +28348,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>XFAB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>X-FAB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -25783,12 +28374,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>INNOLIGHT</t>
+          <t>POET</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Zhongji Innolight</t>
+          <t>POET Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -25809,24 +28400,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SEMCO</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>2</v>
@@ -25835,17 +28426,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SHENGYI</t>
+          <t>NANYA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shengyi Technology</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -25861,17 +28452,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ADVANTEST</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Advantest</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -25887,24 +28478,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BESI</t>
+          <t>SAMBANOVA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BE Semiconductor (Besi)</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
         <v>2</v>
@@ -25913,17 +28504,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IBIDEN</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ibiden</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -25939,232 +28530,232 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>INNOLIGHT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Zhongji Innolight</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
         <v>0</v>
       </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>T_COOL</t>
+          <t>SHENGYI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Liquid Cooling Adoption</t>
+          <t>Shengyi Technology</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Demand Driver / Theme</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="n">
         <v>0</v>
       </c>
-      <c r="E103" t="n">
-        <v>1</v>
-      </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ALPHAWAVE</t>
+          <t>BESI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alphawave Semi</t>
+          <t>BE Semiconductor (Besi)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>IBIDEN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Ibiden</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>HYGON</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Hygon</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>YMTC</t>
+          <t>JX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Yangtze Memory (YMTC)</t>
+          <t>JX Advanced Metals</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>XLIGHT</t>
+          <t>ALCHIP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>XLight</t>
+          <t>Alchip Technologies</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>ZHIPU</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Zhipu AI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>AI Labs / Model Developers</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>T_COOL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cipher Mining</t>
+          <t>Liquid Cooling Adoption</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Demand Driver / Theme</t>
         </is>
       </c>
       <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
         <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -26173,17 +28764,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>ALPHAWAVE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Alphawave Semi</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -26199,17 +28790,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SAMBANOVA</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -26225,24 +28816,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BYTEDANCE</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
         <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>1</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -26251,17 +28842,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LARGAN</t>
+          <t>YMTC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Largan Precision</t>
+          <t>Yangtze Memory (YMTC)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -26277,17 +28868,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>WIWYNN</t>
+          <t>XLIGHT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wiwynn</t>
+          <t>XLight</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -26303,17 +28894,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Camtek</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -26329,24 +28920,24 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Naver</t>
+          <t>Cipher Mining</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hyperscalers / Cloud</t>
+          <t>Datacenter Infrastructure (REITs)</t>
         </is>
       </c>
       <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
         <v>0</v>
-      </c>
-      <c r="E117" t="n">
-        <v>1</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -26355,24 +28946,24 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DOOSAN</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Doosan</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
         <v>0</v>
-      </c>
-      <c r="E118" t="n">
-        <v>1</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -26381,24 +28972,24 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HITACHI</t>
+          <t>BYTEDANCE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
         <v>1</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -26407,17 +28998,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KIOXIA</t>
+          <t>LARGAN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kioxia Holdings</t>
+          <t>Largan Precision</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -26433,24 +29024,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ALLSPACE</t>
+          <t>WIWYNN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ALL.SPACE</t>
+          <t>Wiwynn</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
         <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>1</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -26459,12 +29050,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HANMI</t>
+          <t>CAMT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Hanmi Semiconductor</t>
+          <t>Camtek</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -26485,24 +29076,24 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Naver</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Hyperscalers / Cloud</t>
         </is>
       </c>
       <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
         <v>1</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -26511,24 +29102,24 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>DOOSAN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FormFactor</t>
+          <t>Doosan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
         <v>1</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -26537,17 +29128,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>HITACHI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Optical &amp; Interconnect</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -26563,17 +29154,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>IFX</t>
+          <t>KIOXIA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Kioxia Holdings</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -26589,24 +29180,24 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>ALLSPACE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>ALL.SPACE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
         <v>1</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -26615,17 +29206,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ENR</t>
+          <t>HANMI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Hanmi Semiconductor</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -26641,17 +29232,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DELTA</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Delta Electronics</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -26667,17 +29258,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ASE</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ASE Technology</t>
+          <t>FormFactor</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Semiconductor Equipment</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -26693,12 +29284,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FOCI</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FOCI</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -26719,17 +29310,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>IFX</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -26745,17 +29336,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Memory (HBM/DRAM)</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -26771,17 +29362,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>WOLF</t>
+          <t>ENR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Wolfspeed</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -26797,12 +29388,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>DELTA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Navitas Semiconductor</t>
+          <t>Delta Electronics</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -26823,24 +29414,24 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ASE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>ASE Technology</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chip Designers (Accelerators/Networking)</t>
+          <t>Advanced Packaging / OSAT</t>
         </is>
       </c>
       <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
         <v>0</v>
-      </c>
-      <c r="E136" t="n">
-        <v>1</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
@@ -26849,17 +29440,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TSEM</t>
+          <t>FOCI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tower Semiconductor</t>
+          <t>FOCI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Foundry / Manufacturing</t>
+          <t>Optical &amp; Interconnect</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -26875,17 +29466,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>QUANTA</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Quanta Computer</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -26901,17 +29492,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>WISTRON</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Seagate Technology</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Servers &amp; ODM/OEM</t>
+          <t>Memory (HBM/DRAM)</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -26927,17 +29518,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>WOLF</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Wolfspeed</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Networking Systems</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -26953,17 +29544,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Navitas Semiconductor</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Power Generation / Utilities</t>
+          <t>Power &amp; Cooling Equipment</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -26979,24 +29570,24 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Elite Material</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Chip Designers (Accelerators/Networking)</t>
         </is>
       </c>
       <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
         <v>1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -27005,17 +29596,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>TSEM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Tower Semiconductor</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Foundry / Manufacturing</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -27031,17 +29622,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UNIMICRON</t>
+          <t>QUANTA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Unimicron</t>
+          <t>Quanta Computer</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -27057,17 +29648,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>WISTRON</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Power &amp; Cooling Equipment</t>
+          <t>Servers &amp; ODM/OEM</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -27083,17 +29674,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WULF</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TeraWulf</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Datacenter Infrastructure (REITs)</t>
+          <t>Networking Systems</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -27109,17 +29700,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MURATA</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Murata Manufacturing</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Advanced Packaging / OSAT</t>
+          <t>Power Generation / Utilities</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -27135,12 +29726,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TAIYOYUDEN</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Taiyo Yuden</t>
+          <t>Elite Material</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -27155,6 +29746,292 @@
         <v>0</v>
       </c>
       <c r="F148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>UNIMICRON</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Unimicron</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>onsemi</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Power &amp; Cooling Equipment</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>TeraWulf</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Datacenter Infrastructure (REITs)</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MURATA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Murata Manufacturing</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TAIYOYUDEN</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Taiyo Yuden</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Talen Energy</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Power Generation / Utilities</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Servers &amp; ODM/OEM</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>RXT</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Rackspace Technology</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SK Telecom</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Hyperscalers / Cloud</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>NITTOBO</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Nittobo (Nitto Boseki)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Advanced Packaging / OSAT</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
         <v>1</v>
       </c>
     </row>
